--- a/src/assets/傳票範本_多筆.xlsx
+++ b/src/assets/傳票範本_多筆.xlsx
@@ -9,211 +9,211 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12135" firstSheet="89"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12135" firstSheet="21" activeTab="20"/>
   </bookViews>
   <sheets>
-    <sheet name="工作表 (51)" sheetId="52" r:id="rId1"/>
-    <sheet name="工作表 (52)" sheetId="53" r:id="rId2"/>
-    <sheet name="工作表 (53)" sheetId="54" r:id="rId3"/>
-    <sheet name="工作表 (54)" sheetId="55" r:id="rId4"/>
-    <sheet name="工作表 (55)" sheetId="56" r:id="rId5"/>
-    <sheet name="工作表 (56)" sheetId="57" r:id="rId6"/>
-    <sheet name="工作表 (57)" sheetId="58" r:id="rId7"/>
-    <sheet name="工作表 (58)" sheetId="59" r:id="rId8"/>
-    <sheet name="工作表 (59)" sheetId="60" r:id="rId9"/>
-    <sheet name="工作表 (60)" sheetId="61" r:id="rId10"/>
-    <sheet name="工作表 (61)" sheetId="62" r:id="rId11"/>
-    <sheet name="工作表 (62)" sheetId="63" r:id="rId12"/>
-    <sheet name="工作表 (63)" sheetId="64" r:id="rId13"/>
-    <sheet name="工作表 (64)" sheetId="65" r:id="rId14"/>
-    <sheet name="工作表 (65)" sheetId="66" r:id="rId15"/>
-    <sheet name="工作表 (66)" sheetId="67" r:id="rId16"/>
-    <sheet name="工作表 (67)" sheetId="68" r:id="rId17"/>
-    <sheet name="工作表 (68)" sheetId="69" r:id="rId18"/>
-    <sheet name="工作表 (69)" sheetId="70" r:id="rId19"/>
-    <sheet name="工作表 (70)" sheetId="71" r:id="rId20"/>
-    <sheet name="工作表 (71)" sheetId="72" r:id="rId21"/>
-    <sheet name="工作表 (72)" sheetId="73" r:id="rId22"/>
-    <sheet name="工作表 (73)" sheetId="74" r:id="rId23"/>
-    <sheet name="工作表 (74)" sheetId="75" r:id="rId24"/>
-    <sheet name="工作表 (75)" sheetId="76" r:id="rId25"/>
-    <sheet name="工作表 (76)" sheetId="77" r:id="rId26"/>
-    <sheet name="工作表 (77)" sheetId="78" r:id="rId27"/>
-    <sheet name="工作表 (78)" sheetId="79" r:id="rId28"/>
-    <sheet name="工作表 (79)" sheetId="80" r:id="rId29"/>
-    <sheet name="工作表 (80)" sheetId="81" r:id="rId30"/>
-    <sheet name="工作表 (81)" sheetId="82" r:id="rId31"/>
-    <sheet name="工作表 (82)" sheetId="83" r:id="rId32"/>
-    <sheet name="工作表 (83)" sheetId="84" r:id="rId33"/>
-    <sheet name="工作表 (84)" sheetId="85" r:id="rId34"/>
-    <sheet name="工作表 (85)" sheetId="86" r:id="rId35"/>
-    <sheet name="工作表 (86)" sheetId="87" r:id="rId36"/>
-    <sheet name="工作表 (87)" sheetId="88" r:id="rId37"/>
-    <sheet name="工作表 (88)" sheetId="89" r:id="rId38"/>
-    <sheet name="工作表 (89)" sheetId="90" r:id="rId39"/>
-    <sheet name="工作表 (90)" sheetId="91" r:id="rId40"/>
-    <sheet name="工作表 (91)" sheetId="92" r:id="rId41"/>
-    <sheet name="工作表 (92)" sheetId="93" r:id="rId42"/>
-    <sheet name="工作表 (93)" sheetId="94" r:id="rId43"/>
-    <sheet name="工作表 (94)" sheetId="95" r:id="rId44"/>
-    <sheet name="工作表 (95)" sheetId="96" r:id="rId45"/>
-    <sheet name="工作表 (96)" sheetId="97" r:id="rId46"/>
-    <sheet name="工作表 (97)" sheetId="98" r:id="rId47"/>
-    <sheet name="工作表 (98)" sheetId="99" r:id="rId48"/>
-    <sheet name="工作表 (99)" sheetId="100" r:id="rId49"/>
-    <sheet name="工作表 (100)" sheetId="101" r:id="rId50"/>
-    <sheet name="工作表 (41)" sheetId="42" r:id="rId51"/>
-    <sheet name="工作表 (42)" sheetId="43" r:id="rId52"/>
-    <sheet name="工作表 (43)" sheetId="44" r:id="rId53"/>
-    <sheet name="工作表 (44)" sheetId="45" r:id="rId54"/>
-    <sheet name="工作表 (45)" sheetId="46" r:id="rId55"/>
-    <sheet name="工作表 (46)" sheetId="47" r:id="rId56"/>
-    <sheet name="工作表 (47)" sheetId="48" r:id="rId57"/>
-    <sheet name="工作表 (48)" sheetId="49" r:id="rId58"/>
-    <sheet name="工作表 (49)" sheetId="50" r:id="rId59"/>
-    <sheet name="工作表 (50)" sheetId="51" r:id="rId60"/>
-    <sheet name="工作表 (31)" sheetId="32" r:id="rId61"/>
-    <sheet name="工作表 (32)" sheetId="33" r:id="rId62"/>
-    <sheet name="工作表 (33)" sheetId="34" r:id="rId63"/>
-    <sheet name="工作表 (34)" sheetId="35" r:id="rId64"/>
-    <sheet name="工作表 (35)" sheetId="36" r:id="rId65"/>
-    <sheet name="工作表 (36)" sheetId="37" r:id="rId66"/>
-    <sheet name="工作表 (37)" sheetId="38" r:id="rId67"/>
-    <sheet name="工作表 (38)" sheetId="39" r:id="rId68"/>
-    <sheet name="工作表 (39)" sheetId="40" r:id="rId69"/>
-    <sheet name="工作表 (40)" sheetId="41" r:id="rId70"/>
-    <sheet name="工作表 (21)" sheetId="22" r:id="rId71"/>
-    <sheet name="工作表 (22)" sheetId="23" r:id="rId72"/>
-    <sheet name="工作表 (23)" sheetId="24" r:id="rId73"/>
-    <sheet name="工作表 (24)" sheetId="25" r:id="rId74"/>
-    <sheet name="工作表 (25)" sheetId="26" r:id="rId75"/>
-    <sheet name="工作表 (26)" sheetId="27" r:id="rId76"/>
-    <sheet name="工作表 (27)" sheetId="28" r:id="rId77"/>
-    <sheet name="工作表 (28)" sheetId="29" r:id="rId78"/>
-    <sheet name="工作表 (29)" sheetId="30" r:id="rId79"/>
-    <sheet name="工作表 (30)" sheetId="31" r:id="rId80"/>
-    <sheet name="工作表 (9)" sheetId="10" r:id="rId81"/>
-    <sheet name="工作表 (10)" sheetId="11" r:id="rId82"/>
-    <sheet name="工作表 (5)" sheetId="6" r:id="rId83"/>
-    <sheet name="工作表 (6)" sheetId="7" r:id="rId84"/>
-    <sheet name="工作表 (7)" sheetId="8" r:id="rId85"/>
-    <sheet name="工作表 (8)" sheetId="9" r:id="rId86"/>
-    <sheet name="工作表 (3)" sheetId="4" r:id="rId87"/>
-    <sheet name="工作表 (4)" sheetId="5" r:id="rId88"/>
-    <sheet name="工作表 (2)" sheetId="3" r:id="rId89"/>
-    <sheet name="工作表 (11)" sheetId="12" r:id="rId90"/>
-    <sheet name="工作表 (12)" sheetId="13" r:id="rId91"/>
-    <sheet name="工作表 (13)" sheetId="14" r:id="rId92"/>
-    <sheet name="工作表 (14)" sheetId="15" r:id="rId93"/>
-    <sheet name="工作表 (15)" sheetId="16" r:id="rId94"/>
-    <sheet name="工作表 (16)" sheetId="17" r:id="rId95"/>
-    <sheet name="工作表 (17)" sheetId="18" r:id="rId96"/>
-    <sheet name="工作表 (18)" sheetId="19" r:id="rId97"/>
-    <sheet name="工作表 (19)" sheetId="20" r:id="rId98"/>
-    <sheet name="工作表 (20)" sheetId="21" r:id="rId99"/>
-    <sheet name="工作表" sheetId="2" r:id="rId100"/>
+    <sheet name="工作表 (141)" sheetId="142" r:id="rId1"/>
+    <sheet name="工作表 (142)" sheetId="143" r:id="rId2"/>
+    <sheet name="工作表 (143)" sheetId="144" r:id="rId3"/>
+    <sheet name="工作表 (144)" sheetId="145" r:id="rId4"/>
+    <sheet name="工作表 (145)" sheetId="146" r:id="rId5"/>
+    <sheet name="工作表 (146)" sheetId="147" r:id="rId6"/>
+    <sheet name="工作表 (147)" sheetId="148" r:id="rId7"/>
+    <sheet name="工作表 (148)" sheetId="149" r:id="rId8"/>
+    <sheet name="工作表 (149)" sheetId="150" r:id="rId9"/>
+    <sheet name="工作表 (150)" sheetId="151" r:id="rId10"/>
+    <sheet name="工作表 (131)" sheetId="132" r:id="rId11"/>
+    <sheet name="工作表 (132)" sheetId="133" r:id="rId12"/>
+    <sheet name="工作表 (133)" sheetId="134" r:id="rId13"/>
+    <sheet name="工作表 (134)" sheetId="135" r:id="rId14"/>
+    <sheet name="工作表 (135)" sheetId="136" r:id="rId15"/>
+    <sheet name="工作表 (136)" sheetId="137" r:id="rId16"/>
+    <sheet name="工作表 (137)" sheetId="138" r:id="rId17"/>
+    <sheet name="工作表 (138)" sheetId="139" r:id="rId18"/>
+    <sheet name="工作表 (139)" sheetId="140" r:id="rId19"/>
+    <sheet name="工作表 (140)" sheetId="141" r:id="rId20"/>
+    <sheet name="工作表 (91)" sheetId="92" r:id="rId21"/>
+    <sheet name="工作表 (92)" sheetId="93" r:id="rId22"/>
+    <sheet name="工作表 (93)" sheetId="94" r:id="rId23"/>
+    <sheet name="工作表 (94)" sheetId="95" r:id="rId24"/>
+    <sheet name="工作表 (95)" sheetId="96" r:id="rId25"/>
+    <sheet name="工作表 (96)" sheetId="97" r:id="rId26"/>
+    <sheet name="工作表 (97)" sheetId="98" r:id="rId27"/>
+    <sheet name="工作表 (98)" sheetId="99" r:id="rId28"/>
+    <sheet name="工作表 (99)" sheetId="100" r:id="rId29"/>
+    <sheet name="工作表 (100)" sheetId="101" r:id="rId30"/>
+    <sheet name="工作表 (101)" sheetId="102" r:id="rId31"/>
+    <sheet name="工作表 (102)" sheetId="103" r:id="rId32"/>
+    <sheet name="工作表 (103)" sheetId="104" r:id="rId33"/>
+    <sheet name="工作表 (104)" sheetId="105" r:id="rId34"/>
+    <sheet name="工作表 (105)" sheetId="106" r:id="rId35"/>
+    <sheet name="工作表 (106)" sheetId="107" r:id="rId36"/>
+    <sheet name="工作表 (107)" sheetId="108" r:id="rId37"/>
+    <sheet name="工作表 (108)" sheetId="109" r:id="rId38"/>
+    <sheet name="工作表 (109)" sheetId="110" r:id="rId39"/>
+    <sheet name="工作表 (110)" sheetId="111" r:id="rId40"/>
+    <sheet name="工作表 (111)" sheetId="112" r:id="rId41"/>
+    <sheet name="工作表 (112)" sheetId="113" r:id="rId42"/>
+    <sheet name="工作表 (113)" sheetId="114" r:id="rId43"/>
+    <sheet name="工作表 (114)" sheetId="115" r:id="rId44"/>
+    <sheet name="工作表 (115)" sheetId="116" r:id="rId45"/>
+    <sheet name="工作表 (116)" sheetId="117" r:id="rId46"/>
+    <sheet name="工作表 (117)" sheetId="118" r:id="rId47"/>
+    <sheet name="工作表 (118)" sheetId="119" r:id="rId48"/>
+    <sheet name="工作表 (119)" sheetId="120" r:id="rId49"/>
+    <sheet name="工作表 (120)" sheetId="121" r:id="rId50"/>
+    <sheet name="工作表 (121)" sheetId="122" r:id="rId51"/>
+    <sheet name="工作表 (122)" sheetId="123" r:id="rId52"/>
+    <sheet name="工作表 (123)" sheetId="124" r:id="rId53"/>
+    <sheet name="工作表 (124)" sheetId="125" r:id="rId54"/>
+    <sheet name="工作表 (125)" sheetId="126" r:id="rId55"/>
+    <sheet name="工作表 (126)" sheetId="127" r:id="rId56"/>
+    <sheet name="工作表 (127)" sheetId="128" r:id="rId57"/>
+    <sheet name="工作表 (128)" sheetId="129" r:id="rId58"/>
+    <sheet name="工作表 (129)" sheetId="130" r:id="rId59"/>
+    <sheet name="工作表 (130)" sheetId="131" r:id="rId60"/>
+    <sheet name="工作表 (71)" sheetId="72" r:id="rId61"/>
+    <sheet name="工作表 (72)" sheetId="73" r:id="rId62"/>
+    <sheet name="工作表 (73)" sheetId="74" r:id="rId63"/>
+    <sheet name="工作表 (74)" sheetId="75" r:id="rId64"/>
+    <sheet name="工作表 (75)" sheetId="76" r:id="rId65"/>
+    <sheet name="工作表 (76)" sheetId="77" r:id="rId66"/>
+    <sheet name="工作表 (77)" sheetId="78" r:id="rId67"/>
+    <sheet name="工作表 (78)" sheetId="79" r:id="rId68"/>
+    <sheet name="工作表 (79)" sheetId="80" r:id="rId69"/>
+    <sheet name="工作表 (80)" sheetId="81" r:id="rId70"/>
+    <sheet name="工作表 (81)" sheetId="82" r:id="rId71"/>
+    <sheet name="工作表 (82)" sheetId="83" r:id="rId72"/>
+    <sheet name="工作表 (83)" sheetId="84" r:id="rId73"/>
+    <sheet name="工作表 (84)" sheetId="85" r:id="rId74"/>
+    <sheet name="工作表 (85)" sheetId="86" r:id="rId75"/>
+    <sheet name="工作表 (86)" sheetId="87" r:id="rId76"/>
+    <sheet name="工作表 (87)" sheetId="88" r:id="rId77"/>
+    <sheet name="工作表 (88)" sheetId="89" r:id="rId78"/>
+    <sheet name="工作表 (89)" sheetId="90" r:id="rId79"/>
+    <sheet name="工作表 (90)" sheetId="91" r:id="rId80"/>
+    <sheet name="工作表 (61)" sheetId="62" r:id="rId81"/>
+    <sheet name="工作表 (62)" sheetId="63" r:id="rId82"/>
+    <sheet name="工作表 (63)" sheetId="64" r:id="rId83"/>
+    <sheet name="工作表 (64)" sheetId="65" r:id="rId84"/>
+    <sheet name="工作表 (65)" sheetId="66" r:id="rId85"/>
+    <sheet name="工作表 (66)" sheetId="67" r:id="rId86"/>
+    <sheet name="工作表 (67)" sheetId="68" r:id="rId87"/>
+    <sheet name="工作表 (68)" sheetId="69" r:id="rId88"/>
+    <sheet name="工作表 (69)" sheetId="70" r:id="rId89"/>
+    <sheet name="工作表 (70)" sheetId="71" r:id="rId90"/>
+    <sheet name="工作表 (59)" sheetId="60" r:id="rId91"/>
+    <sheet name="工作表 (60)" sheetId="61" r:id="rId92"/>
+    <sheet name="工作表 (57)" sheetId="58" r:id="rId93"/>
+    <sheet name="工作表 (58)" sheetId="59" r:id="rId94"/>
+    <sheet name="工作表 (55)" sheetId="56" r:id="rId95"/>
+    <sheet name="工作表 (56)" sheetId="57" r:id="rId96"/>
+    <sheet name="工作表 (53)" sheetId="54" r:id="rId97"/>
+    <sheet name="工作表 (54)" sheetId="55" r:id="rId98"/>
+    <sheet name="工作表 (52)" sheetId="53" r:id="rId99"/>
+    <sheet name="工作表 (51)" sheetId="52" r:id="rId100"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Titles" localSheetId="99">工作表!$9:$9</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="81">'工作表 (10)'!$9:$9</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="49">'工作表 (100)'!$9:$9</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="89">'工作表 (11)'!$9:$9</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="90">'工作表 (12)'!$9:$9</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="91">'工作表 (13)'!$9:$9</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="92">'工作表 (14)'!$9:$9</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="93">'工作表 (15)'!$9:$9</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="94">'工作表 (16)'!$9:$9</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="95">'工作表 (17)'!$9:$9</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="96">'工作表 (18)'!$9:$9</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="97">'工作表 (19)'!$9:$9</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="88">'工作表 (2)'!$9:$9</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="98">'工作表 (20)'!$9:$9</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="70">'工作表 (21)'!$9:$9</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="71">'工作表 (22)'!$9:$9</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="72">'工作表 (23)'!$9:$9</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="73">'工作表 (24)'!$9:$9</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="74">'工作表 (25)'!$9:$9</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="75">'工作表 (26)'!$9:$9</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="76">'工作表 (27)'!$9:$9</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="77">'工作表 (28)'!$9:$9</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="78">'工作表 (29)'!$9:$9</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="86">'工作表 (3)'!$9:$9</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="79">'工作表 (30)'!$9:$9</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="60">'工作表 (31)'!$9:$9</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="61">'工作表 (32)'!$9:$9</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="62">'工作表 (33)'!$9:$9</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="63">'工作表 (34)'!$9:$9</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="64">'工作表 (35)'!$9:$9</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="65">'工作表 (36)'!$9:$9</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="66">'工作表 (37)'!$9:$9</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="67">'工作表 (38)'!$9:$9</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="68">'工作表 (39)'!$9:$9</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="87">'工作表 (4)'!$9:$9</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="69">'工作表 (40)'!$9:$9</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="50">'工作表 (41)'!$9:$9</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="51">'工作表 (42)'!$9:$9</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="52">'工作表 (43)'!$9:$9</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="53">'工作表 (44)'!$9:$9</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="54">'工作表 (45)'!$9:$9</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="55">'工作表 (46)'!$9:$9</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="56">'工作表 (47)'!$9:$9</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="57">'工作表 (48)'!$9:$9</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="58">'工作表 (49)'!$9:$9</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="82">'工作表 (5)'!$9:$9</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="59">'工作表 (50)'!$9:$9</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="0">'工作表 (51)'!$9:$9</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="1">'工作表 (52)'!$9:$9</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="2">'工作表 (53)'!$9:$9</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="3">'工作表 (54)'!$9:$9</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="4">'工作表 (55)'!$9:$9</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="5">'工作表 (56)'!$9:$9</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="6">'工作表 (57)'!$9:$9</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="7">'工作表 (58)'!$9:$9</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="8">'工作表 (59)'!$9:$9</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="83">'工作表 (6)'!$9:$9</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="9">'工作表 (60)'!$9:$9</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="10">'工作表 (61)'!$9:$9</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="11">'工作表 (62)'!$9:$9</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="12">'工作表 (63)'!$9:$9</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="13">'工作表 (64)'!$9:$9</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="14">'工作表 (65)'!$9:$9</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="15">'工作表 (66)'!$9:$9</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="16">'工作表 (67)'!$9:$9</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="17">'工作表 (68)'!$9:$9</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="18">'工作表 (69)'!$9:$9</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="84">'工作表 (7)'!$9:$9</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="19">'工作表 (70)'!$9:$9</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="20">'工作表 (71)'!$9:$9</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="21">'工作表 (72)'!$9:$9</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="22">'工作表 (73)'!$9:$9</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="23">'工作表 (74)'!$9:$9</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="24">'工作表 (75)'!$9:$9</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="25">'工作表 (76)'!$9:$9</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="26">'工作表 (77)'!$9:$9</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="27">'工作表 (78)'!$9:$9</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="28">'工作表 (79)'!$9:$9</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="85">'工作表 (8)'!$9:$9</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="29">'工作表 (80)'!$9:$9</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="30">'工作表 (81)'!$9:$9</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="31">'工作表 (82)'!$9:$9</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="32">'工作表 (83)'!$9:$9</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="33">'工作表 (84)'!$9:$9</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="34">'工作表 (85)'!$9:$9</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="35">'工作表 (86)'!$9:$9</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="36">'工作表 (87)'!$9:$9</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="37">'工作表 (88)'!$9:$9</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="38">'工作表 (89)'!$9:$9</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="80">'工作表 (9)'!$9:$9</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="39">'工作表 (90)'!$9:$9</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="40">'工作表 (91)'!$9:$9</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="41">'工作表 (92)'!$9:$9</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="42">'工作表 (93)'!$9:$9</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="43">'工作表 (94)'!$9:$9</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="44">'工作表 (95)'!$9:$9</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="45">'工作表 (96)'!$9:$9</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="46">'工作表 (97)'!$9:$9</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="47">'工作表 (98)'!$9:$9</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="48">'工作表 (99)'!$9:$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="29">'工作表 (100)'!$4:$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="30">'工作表 (101)'!$4:$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="31">'工作表 (102)'!$4:$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="32">'工作表 (103)'!$4:$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="33">'工作表 (104)'!$4:$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="34">'工作表 (105)'!$4:$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="35">'工作表 (106)'!$4:$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="36">'工作表 (107)'!$4:$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="37">'工作表 (108)'!$4:$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="38">'工作表 (109)'!$4:$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="39">'工作表 (110)'!$4:$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="40">'工作表 (111)'!$4:$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="41">'工作表 (112)'!$4:$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="42">'工作表 (113)'!$4:$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="43">'工作表 (114)'!$4:$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="44">'工作表 (115)'!$4:$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="45">'工作表 (116)'!$4:$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="46">'工作表 (117)'!$4:$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="47">'工作表 (118)'!$4:$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="48">'工作表 (119)'!$4:$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="49">'工作表 (120)'!$4:$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="50">'工作表 (121)'!$4:$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="51">'工作表 (122)'!$4:$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="52">'工作表 (123)'!$4:$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="53">'工作表 (124)'!$4:$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="54">'工作表 (125)'!$4:$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="55">'工作表 (126)'!$4:$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="56">'工作表 (127)'!$4:$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="57">'工作表 (128)'!$4:$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="58">'工作表 (129)'!$4:$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="59">'工作表 (130)'!$4:$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="10">'工作表 (131)'!$4:$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="11">'工作表 (132)'!$4:$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="12">'工作表 (133)'!$4:$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="13">'工作表 (134)'!$4:$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="14">'工作表 (135)'!$4:$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="15">'工作表 (136)'!$4:$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="16">'工作表 (137)'!$4:$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="17">'工作表 (138)'!$4:$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="18">'工作表 (139)'!$4:$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="19">'工作表 (140)'!$4:$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'工作表 (141)'!$4:$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'工作表 (142)'!$4:$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'工作表 (143)'!$4:$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'工作表 (144)'!$4:$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">'工作表 (145)'!$4:$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="5">'工作表 (146)'!$4:$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="6">'工作表 (147)'!$4:$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="7">'工作表 (148)'!$4:$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="8">'工作表 (149)'!$4:$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="9">'工作表 (150)'!$4:$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="99">'工作表 (51)'!$4:$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="98">'工作表 (52)'!$4:$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="96">'工作表 (53)'!$4:$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="97">'工作表 (54)'!$4:$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="94">'工作表 (55)'!$4:$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="95">'工作表 (56)'!$4:$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="92">'工作表 (57)'!$4:$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="93">'工作表 (58)'!$4:$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="90">'工作表 (59)'!$4:$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="91">'工作表 (60)'!$4:$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="80">'工作表 (61)'!$4:$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="81">'工作表 (62)'!$4:$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="82">'工作表 (63)'!$4:$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="83">'工作表 (64)'!$4:$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="84">'工作表 (65)'!$4:$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="85">'工作表 (66)'!$4:$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="86">'工作表 (67)'!$4:$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="87">'工作表 (68)'!$4:$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="88">'工作表 (69)'!$4:$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="89">'工作表 (70)'!$4:$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="60">'工作表 (71)'!$4:$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="61">'工作表 (72)'!$4:$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="62">'工作表 (73)'!$4:$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="63">'工作表 (74)'!$4:$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="64">'工作表 (75)'!$4:$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="65">'工作表 (76)'!$4:$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="66">'工作表 (77)'!$4:$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="67">'工作表 (78)'!$4:$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="68">'工作表 (79)'!$4:$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="69">'工作表 (80)'!$4:$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="70">'工作表 (81)'!$4:$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="71">'工作表 (82)'!$4:$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="72">'工作表 (83)'!$4:$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="73">'工作表 (84)'!$4:$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="74">'工作表 (85)'!$4:$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="75">'工作表 (86)'!$4:$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="76">'工作表 (87)'!$4:$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="77">'工作表 (88)'!$4:$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="78">'工作表 (89)'!$4:$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="79">'工作表 (90)'!$4:$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="20">'工作表 (91)'!$4:$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="21">'工作表 (92)'!$4:$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="22">'工作表 (93)'!$4:$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="23">'工作表 (94)'!$4:$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="24">'工作表 (95)'!$4:$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="25">'工作表 (96)'!$4:$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="26">'工作表 (97)'!$4:$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="27">'工作表 (98)'!$4:$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="28">'工作表 (99)'!$4:$9</definedName>
   </definedNames>
   <calcPr calcId="162913" calcMode="manual"/>
   <extLst>
@@ -485,8 +485,17 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -495,16 +504,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -807,8 +807,8 @@
   <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11" style="5" customWidth="1"/>
-    <col min="2" max="2" width="5.625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="11" style="2" customWidth="1"/>
+    <col min="2" max="2" width="5.625" style="2" customWidth="1"/>
     <col min="3" max="3" width="38.875" style="1" customWidth="1"/>
     <col min="4" max="4" width="22.625" style="1" customWidth="1"/>
     <col min="5" max="5" width="11.625" style="1" customWidth="1"/>
@@ -852,7 +852,7 @@
       <c r="H3" s="7"/>
     </row>
     <row r="4" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="12"/>
@@ -862,7 +862,7 @@
       </c>
     </row>
     <row r="5" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="13"/>
@@ -872,7 +872,7 @@
       </c>
     </row>
     <row r="6" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="14"/>
@@ -890,13 +890,13 @@
       <c r="D8" s="9"/>
     </row>
     <row r="9" spans="1:8" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="6" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="10" t="s">
@@ -904,10 +904,264 @@
       </c>
       <c r="E9" s="10"/>
       <c r="F9" s="10"/>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B6:D7"/>
+    <mergeCell ref="D9:F9"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.39370078740157483" bottom="0.39370078740157483" header="0.19685039370078741" footer="0.19685039370078741"/>
+  <pageSetup paperSize="11" scale="70" orientation="landscape" r:id="rId1"/>
+  <headerFooter>
+    <oddHeader>&amp;R&amp;"新細明體,標準"頁次：&amp;"Times New Roman,標準"&amp;P/&amp;N</oddHeader>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:H9"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="11" style="2" customWidth="1"/>
+    <col min="2" max="2" width="5.625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="38.875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="22.625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="11.625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="28.375" style="1" customWidth="1"/>
+    <col min="7" max="8" width="11.625" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="21" x14ac:dyDescent="0.25">
+      <c r="A1" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="11"/>
+    </row>
+    <row r="2" spans="1:8" ht="21" x14ac:dyDescent="0.25">
+      <c r="A2" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="11"/>
+      <c r="C2" s="11"/>
+      <c r="D2" s="11"/>
+      <c r="E2" s="11"/>
+      <c r="F2" s="11"/>
+      <c r="G2" s="11"/>
+      <c r="H2" s="11"/>
+    </row>
+    <row r="3" spans="1:8" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A3" s="7"/>
+      <c r="B3" s="7"/>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7"/>
+      <c r="H3" s="7"/>
+    </row>
+    <row r="4" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="12"/>
+      <c r="C4" s="12"/>
+      <c r="E4" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="13"/>
+      <c r="C5" s="13"/>
+      <c r="E5" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="14"/>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B7" s="14"/>
+      <c r="C7" s="14"/>
+      <c r="D7" s="14"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B8" s="9"/>
+      <c r="C8" s="9"/>
+      <c r="D8" s="9"/>
+    </row>
+    <row r="9" spans="1:8" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E9" s="10"/>
+      <c r="F9" s="10"/>
+      <c r="G9" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B6:D7"/>
+    <mergeCell ref="D9:F9"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.39370078740157483" bottom="0.39370078740157483" header="0.19685039370078741" footer="0.19685039370078741"/>
+  <pageSetup paperSize="11" scale="70" orientation="landscape" r:id="rId1"/>
+  <headerFooter>
+    <oddHeader>&amp;R&amp;"新細明體,標準"頁次：&amp;"Times New Roman,標準"&amp;P/&amp;N</oddHeader>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet100.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:H9"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="11" style="2" customWidth="1"/>
+    <col min="2" max="2" width="5.625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="38.875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="22.625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="11.625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="28.375" style="1" customWidth="1"/>
+    <col min="7" max="8" width="11.625" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="21" x14ac:dyDescent="0.25">
+      <c r="A1" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="11"/>
+    </row>
+    <row r="2" spans="1:8" ht="21" x14ac:dyDescent="0.25">
+      <c r="A2" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="11"/>
+      <c r="C2" s="11"/>
+      <c r="D2" s="11"/>
+      <c r="E2" s="11"/>
+      <c r="F2" s="11"/>
+      <c r="G2" s="11"/>
+      <c r="H2" s="11"/>
+    </row>
+    <row r="3" spans="1:8" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A3" s="3"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+    </row>
+    <row r="4" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="12"/>
+      <c r="C4" s="12"/>
+      <c r="E4" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="13"/>
+      <c r="C5" s="13"/>
+      <c r="E5" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="14"/>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B7" s="14"/>
+      <c r="C7" s="14"/>
+      <c r="D7" s="14"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B8" s="5"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="5"/>
+    </row>
+    <row r="9" spans="1:8" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E9" s="10"/>
+      <c r="F9" s="10"/>
+      <c r="G9" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H9" s="4" t="s">
         <v>12</v>
       </c>
     </row>
@@ -929,13 +1183,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11" style="5" customWidth="1"/>
-    <col min="2" max="2" width="5.625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="11" style="2" customWidth="1"/>
+    <col min="2" max="2" width="5.625" style="2" customWidth="1"/>
     <col min="3" max="3" width="38.875" style="1" customWidth="1"/>
     <col min="4" max="4" width="22.625" style="1" customWidth="1"/>
     <col min="5" max="5" width="11.625" style="1" customWidth="1"/>
@@ -979,7 +1233,7 @@
       <c r="H3" s="7"/>
     </row>
     <row r="4" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="12"/>
@@ -989,7 +1243,7 @@
       </c>
     </row>
     <row r="5" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="13"/>
@@ -999,7 +1253,7 @@
       </c>
     </row>
     <row r="6" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="14"/>
@@ -1017,13 +1271,13 @@
       <c r="D8" s="9"/>
     </row>
     <row r="9" spans="1:8" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="6" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="10" t="s">
@@ -1031,137 +1285,10 @@
       </c>
       <c r="E9" s="10"/>
       <c r="F9" s="10"/>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="H9" s="8" t="s">
-        <v>12</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="D9:F9"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B6:D7"/>
-  </mergeCells>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.39370078740157483" bottom="0.39370078740157483" header="0.19685039370078741" footer="0.19685039370078741"/>
-  <pageSetup paperSize="11" scale="70" orientation="landscape" r:id="rId1"/>
-  <headerFooter>
-    <oddHeader>&amp;R&amp;"新細明體,標準"頁次：&amp;"Times New Roman,標準"&amp;P/&amp;N</oddHeader>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet100.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H9"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="11" style="5" customWidth="1"/>
-    <col min="2" max="2" width="5.625" style="5" customWidth="1"/>
-    <col min="3" max="3" width="38.875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="22.625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="11.625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="28.375" style="1" customWidth="1"/>
-    <col min="7" max="8" width="11.625" style="1" customWidth="1"/>
-    <col min="9" max="16384" width="9" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:8" ht="21" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
-      <c r="H1" s="11"/>
-    </row>
-    <row r="2" spans="1:8" ht="21" x14ac:dyDescent="0.25">
-      <c r="A2" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="11"/>
-      <c r="C2" s="11"/>
-      <c r="D2" s="11"/>
-      <c r="E2" s="11"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="11"/>
-      <c r="H2" s="11"/>
-    </row>
-    <row r="3" spans="1:8" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="A3" s="4"/>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4"/>
-      <c r="H3" s="4"/>
-    </row>
-    <row r="4" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12"/>
-      <c r="E4" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="13"/>
-      <c r="C5" s="13"/>
-      <c r="E5" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" s="14"/>
-      <c r="C6" s="14"/>
-      <c r="D6" s="14"/>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B7" s="14"/>
-      <c r="C7" s="14"/>
-      <c r="D7" s="14"/>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B8" s="6"/>
-      <c r="C8" s="6"/>
-      <c r="D8" s="6"/>
-    </row>
-    <row r="9" spans="1:8" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D9" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="E9" s="10"/>
-      <c r="F9" s="10"/>
-      <c r="G9" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="H9" s="2" t="s">
+      <c r="H9" s="6" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1171,135 +1298,8 @@
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B6:D7"/>
     <mergeCell ref="D9:F9"/>
-    <mergeCell ref="B6:D7"/>
-  </mergeCells>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.39370078740157483" bottom="0.39370078740157483" header="0.19685039370078741" footer="0.19685039370078741"/>
-  <pageSetup paperSize="11" scale="70" orientation="landscape" r:id="rId1"/>
-  <headerFooter>
-    <oddHeader>&amp;R&amp;"新細明體,標準"頁次：&amp;"Times New Roman,標準"&amp;P/&amp;N</oddHeader>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H9"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="11" style="5" customWidth="1"/>
-    <col min="2" max="2" width="5.625" style="5" customWidth="1"/>
-    <col min="3" max="3" width="38.875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="22.625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="11.625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="28.375" style="1" customWidth="1"/>
-    <col min="7" max="8" width="11.625" style="1" customWidth="1"/>
-    <col min="9" max="16384" width="9" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:8" ht="21" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
-      <c r="H1" s="11"/>
-    </row>
-    <row r="2" spans="1:8" ht="21" x14ac:dyDescent="0.25">
-      <c r="A2" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="11"/>
-      <c r="C2" s="11"/>
-      <c r="D2" s="11"/>
-      <c r="E2" s="11"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="11"/>
-      <c r="H2" s="11"/>
-    </row>
-    <row r="3" spans="1:8" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="A3" s="7"/>
-      <c r="B3" s="7"/>
-      <c r="C3" s="7"/>
-      <c r="D3" s="7"/>
-      <c r="E3" s="7"/>
-      <c r="F3" s="7"/>
-      <c r="G3" s="7"/>
-      <c r="H3" s="7"/>
-    </row>
-    <row r="4" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12"/>
-      <c r="E4" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="13"/>
-      <c r="C5" s="13"/>
-      <c r="E5" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" s="14"/>
-      <c r="C6" s="14"/>
-      <c r="D6" s="14"/>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B7" s="14"/>
-      <c r="C7" s="14"/>
-      <c r="D7" s="14"/>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B8" s="9"/>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
-    </row>
-    <row r="9" spans="1:8" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="D9" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="E9" s="10"/>
-      <c r="F9" s="10"/>
-      <c r="G9" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="H9" s="8" t="s">
-        <v>12</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="D9:F9"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B6:D7"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.39370078740157483" bottom="0.39370078740157483" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -1315,8 +1315,8 @@
   <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11" style="5" customWidth="1"/>
-    <col min="2" max="2" width="5.625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="11" style="2" customWidth="1"/>
+    <col min="2" max="2" width="5.625" style="2" customWidth="1"/>
     <col min="3" max="3" width="38.875" style="1" customWidth="1"/>
     <col min="4" max="4" width="22.625" style="1" customWidth="1"/>
     <col min="5" max="5" width="11.625" style="1" customWidth="1"/>
@@ -1360,7 +1360,7 @@
       <c r="H3" s="7"/>
     </row>
     <row r="4" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="12"/>
@@ -1370,7 +1370,7 @@
       </c>
     </row>
     <row r="5" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="13"/>
@@ -1380,7 +1380,7 @@
       </c>
     </row>
     <row r="6" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="14"/>
@@ -1398,13 +1398,13 @@
       <c r="D8" s="9"/>
     </row>
     <row r="9" spans="1:8" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="6" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="10" t="s">
@@ -1412,21 +1412,21 @@
       </c>
       <c r="E9" s="10"/>
       <c r="F9" s="10"/>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="6" t="s">
         <v>12</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="D9:F9"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B6:D7"/>
+    <mergeCell ref="D9:F9"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.39370078740157483" bottom="0.39370078740157483" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -1442,8 +1442,8 @@
   <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11" style="5" customWidth="1"/>
-    <col min="2" max="2" width="5.625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="11" style="2" customWidth="1"/>
+    <col min="2" max="2" width="5.625" style="2" customWidth="1"/>
     <col min="3" max="3" width="38.875" style="1" customWidth="1"/>
     <col min="4" max="4" width="22.625" style="1" customWidth="1"/>
     <col min="5" max="5" width="11.625" style="1" customWidth="1"/>
@@ -1487,17 +1487,17 @@
       <c r="H3" s="7"/>
     </row>
     <row r="4" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
       <c r="E4" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="13"/>
@@ -1507,7 +1507,7 @@
       </c>
     </row>
     <row r="6" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="14"/>
@@ -1525,13 +1525,13 @@
       <c r="D8" s="9"/>
     </row>
     <row r="9" spans="1:8" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="6" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="10" t="s">
@@ -1539,21 +1539,20 @@
       </c>
       <c r="E9" s="10"/>
       <c r="F9" s="10"/>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="6" t="s">
         <v>12</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="D9:F9"/>
+  <mergeCells count="5">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="B4:C4"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B6:D7"/>
+    <mergeCell ref="D9:F9"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.39370078740157483" bottom="0.39370078740157483" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -1569,8 +1568,8 @@
   <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11" style="5" customWidth="1"/>
-    <col min="2" max="2" width="5.625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="11" style="2" customWidth="1"/>
+    <col min="2" max="2" width="5.625" style="2" customWidth="1"/>
     <col min="3" max="3" width="38.875" style="1" customWidth="1"/>
     <col min="4" max="4" width="22.625" style="1" customWidth="1"/>
     <col min="5" max="5" width="11.625" style="1" customWidth="1"/>
@@ -1614,17 +1613,17 @@
       <c r="H3" s="7"/>
     </row>
     <row r="4" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
       <c r="E4" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="13"/>
@@ -1634,7 +1633,7 @@
       </c>
     </row>
     <row r="6" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="14"/>
@@ -1652,13 +1651,13 @@
       <c r="D8" s="9"/>
     </row>
     <row r="9" spans="1:8" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="6" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="10" t="s">
@@ -1666,21 +1665,20 @@
       </c>
       <c r="E9" s="10"/>
       <c r="F9" s="10"/>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="6" t="s">
         <v>12</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="D9:F9"/>
+  <mergeCells count="5">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="B4:C4"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B6:D7"/>
+    <mergeCell ref="D9:F9"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.39370078740157483" bottom="0.39370078740157483" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -1696,8 +1694,8 @@
   <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11" style="5" customWidth="1"/>
-    <col min="2" max="2" width="5.625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="11" style="2" customWidth="1"/>
+    <col min="2" max="2" width="5.625" style="2" customWidth="1"/>
     <col min="3" max="3" width="38.875" style="1" customWidth="1"/>
     <col min="4" max="4" width="22.625" style="1" customWidth="1"/>
     <col min="5" max="5" width="11.625" style="1" customWidth="1"/>
@@ -1741,17 +1739,17 @@
       <c r="H3" s="7"/>
     </row>
     <row r="4" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
       <c r="E4" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="13"/>
@@ -1761,7 +1759,7 @@
       </c>
     </row>
     <row r="6" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="14"/>
@@ -1779,13 +1777,13 @@
       <c r="D8" s="9"/>
     </row>
     <row r="9" spans="1:8" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="6" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="10" t="s">
@@ -1793,21 +1791,20 @@
       </c>
       <c r="E9" s="10"/>
       <c r="F9" s="10"/>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="6" t="s">
         <v>12</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="D9:F9"/>
+  <mergeCells count="5">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="B4:C4"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B6:D7"/>
+    <mergeCell ref="D9:F9"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.39370078740157483" bottom="0.39370078740157483" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -1823,8 +1820,8 @@
   <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11" style="5" customWidth="1"/>
-    <col min="2" max="2" width="5.625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="11" style="2" customWidth="1"/>
+    <col min="2" max="2" width="5.625" style="2" customWidth="1"/>
     <col min="3" max="3" width="38.875" style="1" customWidth="1"/>
     <col min="4" max="4" width="22.625" style="1" customWidth="1"/>
     <col min="5" max="5" width="11.625" style="1" customWidth="1"/>
@@ -1868,17 +1865,17 @@
       <c r="H3" s="7"/>
     </row>
     <row r="4" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
       <c r="E4" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="13"/>
@@ -1888,7 +1885,7 @@
       </c>
     </row>
     <row r="6" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="14"/>
@@ -1906,13 +1903,13 @@
       <c r="D8" s="9"/>
     </row>
     <row r="9" spans="1:8" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="6" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="10" t="s">
@@ -1920,21 +1917,20 @@
       </c>
       <c r="E9" s="10"/>
       <c r="F9" s="10"/>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="6" t="s">
         <v>12</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="D9:F9"/>
+  <mergeCells count="5">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="B4:C4"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B6:D7"/>
+    <mergeCell ref="D9:F9"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.39370078740157483" bottom="0.39370078740157483" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -1950,8 +1946,8 @@
   <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11" style="5" customWidth="1"/>
-    <col min="2" max="2" width="5.625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="11" style="2" customWidth="1"/>
+    <col min="2" max="2" width="5.625" style="2" customWidth="1"/>
     <col min="3" max="3" width="38.875" style="1" customWidth="1"/>
     <col min="4" max="4" width="22.625" style="1" customWidth="1"/>
     <col min="5" max="5" width="11.625" style="1" customWidth="1"/>
@@ -1995,7 +1991,7 @@
       <c r="H3" s="7"/>
     </row>
     <row r="4" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="12"/>
@@ -2005,7 +2001,7 @@
       </c>
     </row>
     <row r="5" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="13"/>
@@ -2015,7 +2011,7 @@
       </c>
     </row>
     <row r="6" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="14"/>
@@ -2033,13 +2029,13 @@
       <c r="D8" s="9"/>
     </row>
     <row r="9" spans="1:8" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="6" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="10" t="s">
@@ -2047,21 +2043,21 @@
       </c>
       <c r="E9" s="10"/>
       <c r="F9" s="10"/>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="6" t="s">
         <v>12</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="D9:F9"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B6:D7"/>
+    <mergeCell ref="D9:F9"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.39370078740157483" bottom="0.39370078740157483" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -2077,8 +2073,8 @@
   <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11" style="5" customWidth="1"/>
-    <col min="2" max="2" width="5.625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="11" style="2" customWidth="1"/>
+    <col min="2" max="2" width="5.625" style="2" customWidth="1"/>
     <col min="3" max="3" width="38.875" style="1" customWidth="1"/>
     <col min="4" max="4" width="22.625" style="1" customWidth="1"/>
     <col min="5" max="5" width="11.625" style="1" customWidth="1"/>
@@ -2122,7 +2118,7 @@
       <c r="H3" s="7"/>
     </row>
     <row r="4" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="12"/>
@@ -2132,7 +2128,7 @@
       </c>
     </row>
     <row r="5" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="13"/>
@@ -2142,7 +2138,7 @@
       </c>
     </row>
     <row r="6" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="14"/>
@@ -2160,13 +2156,13 @@
       <c r="D8" s="9"/>
     </row>
     <row r="9" spans="1:8" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="6" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="10" t="s">
@@ -2174,21 +2170,21 @@
       </c>
       <c r="E9" s="10"/>
       <c r="F9" s="10"/>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="6" t="s">
         <v>12</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="D9:F9"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B6:D7"/>
+    <mergeCell ref="D9:F9"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.39370078740157483" bottom="0.39370078740157483" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -2204,8 +2200,8 @@
   <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11" style="5" customWidth="1"/>
-    <col min="2" max="2" width="5.625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="11" style="2" customWidth="1"/>
+    <col min="2" max="2" width="5.625" style="2" customWidth="1"/>
     <col min="3" max="3" width="38.875" style="1" customWidth="1"/>
     <col min="4" max="4" width="22.625" style="1" customWidth="1"/>
     <col min="5" max="5" width="11.625" style="1" customWidth="1"/>
@@ -2249,7 +2245,7 @@
       <c r="H3" s="7"/>
     </row>
     <row r="4" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="12"/>
@@ -2259,7 +2255,7 @@
       </c>
     </row>
     <row r="5" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="13"/>
@@ -2269,7 +2265,7 @@
       </c>
     </row>
     <row r="6" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="14"/>
@@ -2287,13 +2283,13 @@
       <c r="D8" s="9"/>
     </row>
     <row r="9" spans="1:8" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="6" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="10" t="s">
@@ -2301,21 +2297,21 @@
       </c>
       <c r="E9" s="10"/>
       <c r="F9" s="10"/>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="6" t="s">
         <v>12</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="D9:F9"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B6:D7"/>
+    <mergeCell ref="D9:F9"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.39370078740157483" bottom="0.39370078740157483" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -2331,8 +2327,8 @@
   <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11" style="5" customWidth="1"/>
-    <col min="2" max="2" width="5.625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="11" style="2" customWidth="1"/>
+    <col min="2" max="2" width="5.625" style="2" customWidth="1"/>
     <col min="3" max="3" width="38.875" style="1" customWidth="1"/>
     <col min="4" max="4" width="22.625" style="1" customWidth="1"/>
     <col min="5" max="5" width="11.625" style="1" customWidth="1"/>
@@ -2376,7 +2372,7 @@
       <c r="H3" s="7"/>
     </row>
     <row r="4" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="12"/>
@@ -2386,7 +2382,7 @@
       </c>
     </row>
     <row r="5" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="13"/>
@@ -2396,7 +2392,7 @@
       </c>
     </row>
     <row r="6" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="14"/>
@@ -2414,13 +2410,13 @@
       <c r="D8" s="9"/>
     </row>
     <row r="9" spans="1:8" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="6" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="10" t="s">
@@ -2428,21 +2424,21 @@
       </c>
       <c r="E9" s="10"/>
       <c r="F9" s="10"/>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="6" t="s">
         <v>12</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="D9:F9"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B6:D7"/>
+    <mergeCell ref="D9:F9"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.39370078740157483" bottom="0.39370078740157483" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -2458,8 +2454,8 @@
   <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11" style="5" customWidth="1"/>
-    <col min="2" max="2" width="5.625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="11" style="2" customWidth="1"/>
+    <col min="2" max="2" width="5.625" style="2" customWidth="1"/>
     <col min="3" max="3" width="38.875" style="1" customWidth="1"/>
     <col min="4" max="4" width="22.625" style="1" customWidth="1"/>
     <col min="5" max="5" width="11.625" style="1" customWidth="1"/>
@@ -2503,7 +2499,7 @@
       <c r="H3" s="7"/>
     </row>
     <row r="4" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="12"/>
@@ -2513,7 +2509,7 @@
       </c>
     </row>
     <row r="5" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="13"/>
@@ -2523,7 +2519,7 @@
       </c>
     </row>
     <row r="6" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="14"/>
@@ -2541,13 +2537,13 @@
       <c r="D8" s="9"/>
     </row>
     <row r="9" spans="1:8" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="6" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="10" t="s">
@@ -2555,21 +2551,21 @@
       </c>
       <c r="E9" s="10"/>
       <c r="F9" s="10"/>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="6" t="s">
         <v>12</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="D9:F9"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B6:D7"/>
+    <mergeCell ref="D9:F9"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.39370078740157483" bottom="0.39370078740157483" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -2585,8 +2581,8 @@
   <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11" style="5" customWidth="1"/>
-    <col min="2" max="2" width="5.625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="11" style="2" customWidth="1"/>
+    <col min="2" max="2" width="5.625" style="2" customWidth="1"/>
     <col min="3" max="3" width="38.875" style="1" customWidth="1"/>
     <col min="4" max="4" width="22.625" style="1" customWidth="1"/>
     <col min="5" max="5" width="11.625" style="1" customWidth="1"/>
@@ -2630,7 +2626,7 @@
       <c r="H3" s="7"/>
     </row>
     <row r="4" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="12"/>
@@ -2640,7 +2636,7 @@
       </c>
     </row>
     <row r="5" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="13"/>
@@ -2650,7 +2646,7 @@
       </c>
     </row>
     <row r="6" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="14"/>
@@ -2668,13 +2664,13 @@
       <c r="D8" s="9"/>
     </row>
     <row r="9" spans="1:8" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="6" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="10" t="s">
@@ -2682,21 +2678,21 @@
       </c>
       <c r="E9" s="10"/>
       <c r="F9" s="10"/>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="6" t="s">
         <v>12</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="D9:F9"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B6:D7"/>
+    <mergeCell ref="D9:F9"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.39370078740157483" bottom="0.39370078740157483" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -2712,8 +2708,8 @@
   <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11" style="5" customWidth="1"/>
-    <col min="2" max="2" width="5.625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="11" style="2" customWidth="1"/>
+    <col min="2" max="2" width="5.625" style="2" customWidth="1"/>
     <col min="3" max="3" width="38.875" style="1" customWidth="1"/>
     <col min="4" max="4" width="22.625" style="1" customWidth="1"/>
     <col min="5" max="5" width="11.625" style="1" customWidth="1"/>
@@ -2757,7 +2753,7 @@
       <c r="H3" s="7"/>
     </row>
     <row r="4" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="12"/>
@@ -2767,7 +2763,7 @@
       </c>
     </row>
     <row r="5" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="13"/>
@@ -2777,7 +2773,7 @@
       </c>
     </row>
     <row r="6" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="14"/>
@@ -2795,13 +2791,13 @@
       <c r="D8" s="9"/>
     </row>
     <row r="9" spans="1:8" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="6" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="10" t="s">
@@ -2809,21 +2805,21 @@
       </c>
       <c r="E9" s="10"/>
       <c r="F9" s="10"/>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="6" t="s">
         <v>12</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="D9:F9"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B6:D7"/>
+    <mergeCell ref="D9:F9"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.39370078740157483" bottom="0.39370078740157483" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -2839,8 +2835,8 @@
   <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11" style="5" customWidth="1"/>
-    <col min="2" max="2" width="5.625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="11" style="2" customWidth="1"/>
+    <col min="2" max="2" width="5.625" style="2" customWidth="1"/>
     <col min="3" max="3" width="38.875" style="1" customWidth="1"/>
     <col min="4" max="4" width="22.625" style="1" customWidth="1"/>
     <col min="5" max="5" width="11.625" style="1" customWidth="1"/>
@@ -2884,17 +2880,17 @@
       <c r="H3" s="7"/>
     </row>
     <row r="4" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
       <c r="E4" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="13"/>
@@ -2904,7 +2900,7 @@
       </c>
     </row>
     <row r="6" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="14"/>
@@ -2922,13 +2918,13 @@
       <c r="D8" s="9"/>
     </row>
     <row r="9" spans="1:8" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="6" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="10" t="s">
@@ -2936,21 +2932,20 @@
       </c>
       <c r="E9" s="10"/>
       <c r="F9" s="10"/>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="6" t="s">
         <v>12</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="D9:F9"/>
+  <mergeCells count="5">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="B4:C4"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B6:D7"/>
+    <mergeCell ref="D9:F9"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.39370078740157483" bottom="0.39370078740157483" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -2966,8 +2961,8 @@
   <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11" style="5" customWidth="1"/>
-    <col min="2" max="2" width="5.625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="11" style="2" customWidth="1"/>
+    <col min="2" max="2" width="5.625" style="2" customWidth="1"/>
     <col min="3" max="3" width="38.875" style="1" customWidth="1"/>
     <col min="4" max="4" width="22.625" style="1" customWidth="1"/>
     <col min="5" max="5" width="11.625" style="1" customWidth="1"/>
@@ -3011,17 +3006,17 @@
       <c r="H3" s="7"/>
     </row>
     <row r="4" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
       <c r="E4" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="13"/>
@@ -3031,7 +3026,7 @@
       </c>
     </row>
     <row r="6" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="14"/>
@@ -3049,13 +3044,13 @@
       <c r="D8" s="9"/>
     </row>
     <row r="9" spans="1:8" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="6" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="10" t="s">
@@ -3063,21 +3058,20 @@
       </c>
       <c r="E9" s="10"/>
       <c r="F9" s="10"/>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="6" t="s">
         <v>12</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="D9:F9"/>
+  <mergeCells count="5">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="B4:C4"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B6:D7"/>
+    <mergeCell ref="D9:F9"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.39370078740157483" bottom="0.39370078740157483" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -3093,8 +3087,8 @@
   <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11" style="5" customWidth="1"/>
-    <col min="2" max="2" width="5.625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="11" style="2" customWidth="1"/>
+    <col min="2" max="2" width="5.625" style="2" customWidth="1"/>
     <col min="3" max="3" width="38.875" style="1" customWidth="1"/>
     <col min="4" max="4" width="22.625" style="1" customWidth="1"/>
     <col min="5" max="5" width="11.625" style="1" customWidth="1"/>
@@ -3138,17 +3132,17 @@
       <c r="H3" s="7"/>
     </row>
     <row r="4" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
       <c r="E4" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="13"/>
@@ -3158,7 +3152,7 @@
       </c>
     </row>
     <row r="6" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="14"/>
@@ -3176,13 +3170,13 @@
       <c r="D8" s="9"/>
     </row>
     <row r="9" spans="1:8" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="6" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="10" t="s">
@@ -3190,21 +3184,20 @@
       </c>
       <c r="E9" s="10"/>
       <c r="F9" s="10"/>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="6" t="s">
         <v>12</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="D9:F9"/>
+  <mergeCells count="5">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="B4:C4"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B6:D7"/>
+    <mergeCell ref="D9:F9"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.39370078740157483" bottom="0.39370078740157483" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -3220,8 +3213,8 @@
   <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11" style="5" customWidth="1"/>
-    <col min="2" max="2" width="5.625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="11" style="2" customWidth="1"/>
+    <col min="2" max="2" width="5.625" style="2" customWidth="1"/>
     <col min="3" max="3" width="38.875" style="1" customWidth="1"/>
     <col min="4" max="4" width="22.625" style="1" customWidth="1"/>
     <col min="5" max="5" width="11.625" style="1" customWidth="1"/>
@@ -3265,17 +3258,17 @@
       <c r="H3" s="7"/>
     </row>
     <row r="4" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
       <c r="E4" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="13"/>
@@ -3285,7 +3278,7 @@
       </c>
     </row>
     <row r="6" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="14"/>
@@ -3303,13 +3296,13 @@
       <c r="D8" s="9"/>
     </row>
     <row r="9" spans="1:8" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="6" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="10" t="s">
@@ -3317,21 +3310,20 @@
       </c>
       <c r="E9" s="10"/>
       <c r="F9" s="10"/>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="6" t="s">
         <v>12</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="D9:F9"/>
+  <mergeCells count="5">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="B4:C4"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B6:D7"/>
+    <mergeCell ref="D9:F9"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.39370078740157483" bottom="0.39370078740157483" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -3347,8 +3339,8 @@
   <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11" style="5" customWidth="1"/>
-    <col min="2" max="2" width="5.625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="11" style="2" customWidth="1"/>
+    <col min="2" max="2" width="5.625" style="2" customWidth="1"/>
     <col min="3" max="3" width="38.875" style="1" customWidth="1"/>
     <col min="4" max="4" width="22.625" style="1" customWidth="1"/>
     <col min="5" max="5" width="11.625" style="1" customWidth="1"/>
@@ -3392,7 +3384,7 @@
       <c r="H3" s="7"/>
     </row>
     <row r="4" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="12"/>
@@ -3402,7 +3394,7 @@
       </c>
     </row>
     <row r="5" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="13"/>
@@ -3412,7 +3404,7 @@
       </c>
     </row>
     <row r="6" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="14"/>
@@ -3430,13 +3422,13 @@
       <c r="D8" s="9"/>
     </row>
     <row r="9" spans="1:8" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="6" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="10" t="s">
@@ -3444,21 +3436,21 @@
       </c>
       <c r="E9" s="10"/>
       <c r="F9" s="10"/>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="6" t="s">
         <v>12</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="D9:F9"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B6:D7"/>
+    <mergeCell ref="D9:F9"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.39370078740157483" bottom="0.39370078740157483" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -3474,8 +3466,8 @@
   <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11" style="5" customWidth="1"/>
-    <col min="2" max="2" width="5.625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="11" style="2" customWidth="1"/>
+    <col min="2" max="2" width="5.625" style="2" customWidth="1"/>
     <col min="3" max="3" width="38.875" style="1" customWidth="1"/>
     <col min="4" max="4" width="22.625" style="1" customWidth="1"/>
     <col min="5" max="5" width="11.625" style="1" customWidth="1"/>
@@ -3519,7 +3511,7 @@
       <c r="H3" s="7"/>
     </row>
     <row r="4" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="12"/>
@@ -3529,7 +3521,7 @@
       </c>
     </row>
     <row r="5" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="13"/>
@@ -3539,7 +3531,7 @@
       </c>
     </row>
     <row r="6" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="14"/>
@@ -3557,13 +3549,13 @@
       <c r="D8" s="9"/>
     </row>
     <row r="9" spans="1:8" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="6" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="10" t="s">
@@ -3571,21 +3563,21 @@
       </c>
       <c r="E9" s="10"/>
       <c r="F9" s="10"/>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="6" t="s">
         <v>12</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="D9:F9"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B6:D7"/>
+    <mergeCell ref="D9:F9"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.39370078740157483" bottom="0.39370078740157483" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -3601,8 +3593,8 @@
   <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11" style="5" customWidth="1"/>
-    <col min="2" max="2" width="5.625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="11" style="2" customWidth="1"/>
+    <col min="2" max="2" width="5.625" style="2" customWidth="1"/>
     <col min="3" max="3" width="38.875" style="1" customWidth="1"/>
     <col min="4" max="4" width="22.625" style="1" customWidth="1"/>
     <col min="5" max="5" width="11.625" style="1" customWidth="1"/>
@@ -3646,7 +3638,7 @@
       <c r="H3" s="7"/>
     </row>
     <row r="4" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="12"/>
@@ -3656,7 +3648,7 @@
       </c>
     </row>
     <row r="5" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="13"/>
@@ -3666,7 +3658,7 @@
       </c>
     </row>
     <row r="6" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="14"/>
@@ -3684,13 +3676,13 @@
       <c r="D8" s="9"/>
     </row>
     <row r="9" spans="1:8" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="6" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="10" t="s">
@@ -3698,21 +3690,21 @@
       </c>
       <c r="E9" s="10"/>
       <c r="F9" s="10"/>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="6" t="s">
         <v>12</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="D9:F9"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B6:D7"/>
+    <mergeCell ref="D9:F9"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.39370078740157483" bottom="0.39370078740157483" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -3728,8 +3720,8 @@
   <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11" style="5" customWidth="1"/>
-    <col min="2" max="2" width="5.625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="11" style="2" customWidth="1"/>
+    <col min="2" max="2" width="5.625" style="2" customWidth="1"/>
     <col min="3" max="3" width="38.875" style="1" customWidth="1"/>
     <col min="4" max="4" width="22.625" style="1" customWidth="1"/>
     <col min="5" max="5" width="11.625" style="1" customWidth="1"/>
@@ -3773,17 +3765,17 @@
       <c r="H3" s="7"/>
     </row>
     <row r="4" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
       <c r="E4" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="13"/>
@@ -3793,7 +3785,7 @@
       </c>
     </row>
     <row r="6" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="14"/>
@@ -3811,13 +3803,13 @@
       <c r="D8" s="9"/>
     </row>
     <row r="9" spans="1:8" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="6" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="10" t="s">
@@ -3825,21 +3817,20 @@
       </c>
       <c r="E9" s="10"/>
       <c r="F9" s="10"/>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="6" t="s">
         <v>12</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="D9:F9"/>
+  <mergeCells count="5">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="B4:C4"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B6:D7"/>
+    <mergeCell ref="D9:F9"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.39370078740157483" bottom="0.39370078740157483" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -3855,8 +3846,8 @@
   <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11" style="5" customWidth="1"/>
-    <col min="2" max="2" width="5.625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="11" style="2" customWidth="1"/>
+    <col min="2" max="2" width="5.625" style="2" customWidth="1"/>
     <col min="3" max="3" width="38.875" style="1" customWidth="1"/>
     <col min="4" max="4" width="22.625" style="1" customWidth="1"/>
     <col min="5" max="5" width="11.625" style="1" customWidth="1"/>
@@ -3900,7 +3891,7 @@
       <c r="H3" s="7"/>
     </row>
     <row r="4" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="12"/>
@@ -3910,7 +3901,7 @@
       </c>
     </row>
     <row r="5" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="13"/>
@@ -3920,7 +3911,7 @@
       </c>
     </row>
     <row r="6" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="14"/>
@@ -3938,13 +3929,13 @@
       <c r="D8" s="9"/>
     </row>
     <row r="9" spans="1:8" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="6" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="10" t="s">
@@ -3952,21 +3943,21 @@
       </c>
       <c r="E9" s="10"/>
       <c r="F9" s="10"/>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="6" t="s">
         <v>12</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="D9:F9"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B6:D7"/>
+    <mergeCell ref="D9:F9"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.39370078740157483" bottom="0.39370078740157483" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -3982,8 +3973,8 @@
   <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11" style="5" customWidth="1"/>
-    <col min="2" max="2" width="5.625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="11" style="2" customWidth="1"/>
+    <col min="2" max="2" width="5.625" style="2" customWidth="1"/>
     <col min="3" max="3" width="38.875" style="1" customWidth="1"/>
     <col min="4" max="4" width="22.625" style="1" customWidth="1"/>
     <col min="5" max="5" width="11.625" style="1" customWidth="1"/>
@@ -4027,7 +4018,7 @@
       <c r="H3" s="7"/>
     </row>
     <row r="4" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="12"/>
@@ -4037,7 +4028,7 @@
       </c>
     </row>
     <row r="5" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="13"/>
@@ -4047,7 +4038,7 @@
       </c>
     </row>
     <row r="6" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="14"/>
@@ -4065,13 +4056,13 @@
       <c r="D8" s="9"/>
     </row>
     <row r="9" spans="1:8" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="6" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="10" t="s">
@@ -4079,21 +4070,21 @@
       </c>
       <c r="E9" s="10"/>
       <c r="F9" s="10"/>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="6" t="s">
         <v>12</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="D9:F9"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B6:D7"/>
+    <mergeCell ref="D9:F9"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.39370078740157483" bottom="0.39370078740157483" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -4109,8 +4100,8 @@
   <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11" style="5" customWidth="1"/>
-    <col min="2" max="2" width="5.625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="11" style="2" customWidth="1"/>
+    <col min="2" max="2" width="5.625" style="2" customWidth="1"/>
     <col min="3" max="3" width="38.875" style="1" customWidth="1"/>
     <col min="4" max="4" width="22.625" style="1" customWidth="1"/>
     <col min="5" max="5" width="11.625" style="1" customWidth="1"/>
@@ -4154,7 +4145,7 @@
       <c r="H3" s="7"/>
     </row>
     <row r="4" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="12"/>
@@ -4164,7 +4155,7 @@
       </c>
     </row>
     <row r="5" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="13"/>
@@ -4174,7 +4165,7 @@
       </c>
     </row>
     <row r="6" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="14"/>
@@ -4192,13 +4183,13 @@
       <c r="D8" s="9"/>
     </row>
     <row r="9" spans="1:8" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="6" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="10" t="s">
@@ -4206,21 +4197,21 @@
       </c>
       <c r="E9" s="10"/>
       <c r="F9" s="10"/>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="6" t="s">
         <v>12</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="D9:F9"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B6:D7"/>
+    <mergeCell ref="D9:F9"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.39370078740157483" bottom="0.39370078740157483" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -4236,8 +4227,8 @@
   <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11" style="5" customWidth="1"/>
-    <col min="2" max="2" width="5.625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="11" style="2" customWidth="1"/>
+    <col min="2" max="2" width="5.625" style="2" customWidth="1"/>
     <col min="3" max="3" width="38.875" style="1" customWidth="1"/>
     <col min="4" max="4" width="22.625" style="1" customWidth="1"/>
     <col min="5" max="5" width="11.625" style="1" customWidth="1"/>
@@ -4281,17 +4272,17 @@
       <c r="H3" s="7"/>
     </row>
     <row r="4" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
       <c r="E4" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="13"/>
@@ -4301,7 +4292,7 @@
       </c>
     </row>
     <row r="6" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="14"/>
@@ -4319,13 +4310,13 @@
       <c r="D8" s="9"/>
     </row>
     <row r="9" spans="1:8" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="6" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="10" t="s">
@@ -4333,21 +4324,20 @@
       </c>
       <c r="E9" s="10"/>
       <c r="F9" s="10"/>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="6" t="s">
         <v>12</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="D9:F9"/>
+  <mergeCells count="5">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="B4:C4"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B6:D7"/>
+    <mergeCell ref="D9:F9"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.39370078740157483" bottom="0.39370078740157483" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -4363,8 +4353,8 @@
   <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11" style="5" customWidth="1"/>
-    <col min="2" max="2" width="5.625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="11" style="2" customWidth="1"/>
+    <col min="2" max="2" width="5.625" style="2" customWidth="1"/>
     <col min="3" max="3" width="38.875" style="1" customWidth="1"/>
     <col min="4" max="4" width="22.625" style="1" customWidth="1"/>
     <col min="5" max="5" width="11.625" style="1" customWidth="1"/>
@@ -4408,17 +4398,17 @@
       <c r="H3" s="7"/>
     </row>
     <row r="4" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
       <c r="E4" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="13"/>
@@ -4428,7 +4418,7 @@
       </c>
     </row>
     <row r="6" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="14"/>
@@ -4446,13 +4436,13 @@
       <c r="D8" s="9"/>
     </row>
     <row r="9" spans="1:8" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="6" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="10" t="s">
@@ -4460,21 +4450,20 @@
       </c>
       <c r="E9" s="10"/>
       <c r="F9" s="10"/>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="6" t="s">
         <v>12</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="D9:F9"/>
+  <mergeCells count="5">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="B4:C4"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B6:D7"/>
+    <mergeCell ref="D9:F9"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.39370078740157483" bottom="0.39370078740157483" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -4490,8 +4479,8 @@
   <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11" style="5" customWidth="1"/>
-    <col min="2" max="2" width="5.625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="11" style="2" customWidth="1"/>
+    <col min="2" max="2" width="5.625" style="2" customWidth="1"/>
     <col min="3" max="3" width="38.875" style="1" customWidth="1"/>
     <col min="4" max="4" width="22.625" style="1" customWidth="1"/>
     <col min="5" max="5" width="11.625" style="1" customWidth="1"/>
@@ -4535,17 +4524,17 @@
       <c r="H3" s="7"/>
     </row>
     <row r="4" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
       <c r="E4" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="13"/>
@@ -4555,7 +4544,7 @@
       </c>
     </row>
     <row r="6" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="14"/>
@@ -4573,13 +4562,13 @@
       <c r="D8" s="9"/>
     </row>
     <row r="9" spans="1:8" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="6" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="10" t="s">
@@ -4587,21 +4576,20 @@
       </c>
       <c r="E9" s="10"/>
       <c r="F9" s="10"/>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="6" t="s">
         <v>12</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="D9:F9"/>
+  <mergeCells count="5">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="B4:C4"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B6:D7"/>
+    <mergeCell ref="D9:F9"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.39370078740157483" bottom="0.39370078740157483" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -4617,8 +4605,8 @@
   <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11" style="5" customWidth="1"/>
-    <col min="2" max="2" width="5.625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="11" style="2" customWidth="1"/>
+    <col min="2" max="2" width="5.625" style="2" customWidth="1"/>
     <col min="3" max="3" width="38.875" style="1" customWidth="1"/>
     <col min="4" max="4" width="22.625" style="1" customWidth="1"/>
     <col min="5" max="5" width="11.625" style="1" customWidth="1"/>
@@ -4662,17 +4650,17 @@
       <c r="H3" s="7"/>
     </row>
     <row r="4" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
       <c r="E4" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="13"/>
@@ -4682,7 +4670,7 @@
       </c>
     </row>
     <row r="6" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="14"/>
@@ -4700,13 +4688,13 @@
       <c r="D8" s="9"/>
     </row>
     <row r="9" spans="1:8" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="6" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="10" t="s">
@@ -4714,21 +4702,20 @@
       </c>
       <c r="E9" s="10"/>
       <c r="F9" s="10"/>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="6" t="s">
         <v>12</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="D9:F9"/>
+  <mergeCells count="5">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="B4:C4"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B6:D7"/>
+    <mergeCell ref="D9:F9"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.39370078740157483" bottom="0.39370078740157483" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -4744,8 +4731,8 @@
   <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11" style="5" customWidth="1"/>
-    <col min="2" max="2" width="5.625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="11" style="2" customWidth="1"/>
+    <col min="2" max="2" width="5.625" style="2" customWidth="1"/>
     <col min="3" max="3" width="38.875" style="1" customWidth="1"/>
     <col min="4" max="4" width="22.625" style="1" customWidth="1"/>
     <col min="5" max="5" width="11.625" style="1" customWidth="1"/>
@@ -4789,7 +4776,7 @@
       <c r="H3" s="7"/>
     </row>
     <row r="4" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="12"/>
@@ -4799,7 +4786,7 @@
       </c>
     </row>
     <row r="5" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="13"/>
@@ -4809,7 +4796,7 @@
       </c>
     </row>
     <row r="6" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="14"/>
@@ -4827,13 +4814,13 @@
       <c r="D8" s="9"/>
     </row>
     <row r="9" spans="1:8" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="6" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="10" t="s">
@@ -4841,21 +4828,21 @@
       </c>
       <c r="E9" s="10"/>
       <c r="F9" s="10"/>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="6" t="s">
         <v>12</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="D9:F9"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B6:D7"/>
+    <mergeCell ref="D9:F9"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.39370078740157483" bottom="0.39370078740157483" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -4871,8 +4858,8 @@
   <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11" style="5" customWidth="1"/>
-    <col min="2" max="2" width="5.625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="11" style="2" customWidth="1"/>
+    <col min="2" max="2" width="5.625" style="2" customWidth="1"/>
     <col min="3" max="3" width="38.875" style="1" customWidth="1"/>
     <col min="4" max="4" width="22.625" style="1" customWidth="1"/>
     <col min="5" max="5" width="11.625" style="1" customWidth="1"/>
@@ -4916,7 +4903,7 @@
       <c r="H3" s="7"/>
     </row>
     <row r="4" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="12"/>
@@ -4926,7 +4913,7 @@
       </c>
     </row>
     <row r="5" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="13"/>
@@ -4936,7 +4923,7 @@
       </c>
     </row>
     <row r="6" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="14"/>
@@ -4954,13 +4941,13 @@
       <c r="D8" s="9"/>
     </row>
     <row r="9" spans="1:8" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="6" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="10" t="s">
@@ -4968,21 +4955,21 @@
       </c>
       <c r="E9" s="10"/>
       <c r="F9" s="10"/>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="6" t="s">
         <v>12</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="D9:F9"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B6:D7"/>
+    <mergeCell ref="D9:F9"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.39370078740157483" bottom="0.39370078740157483" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -4998,8 +4985,8 @@
   <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11" style="5" customWidth="1"/>
-    <col min="2" max="2" width="5.625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="11" style="2" customWidth="1"/>
+    <col min="2" max="2" width="5.625" style="2" customWidth="1"/>
     <col min="3" max="3" width="38.875" style="1" customWidth="1"/>
     <col min="4" max="4" width="22.625" style="1" customWidth="1"/>
     <col min="5" max="5" width="11.625" style="1" customWidth="1"/>
@@ -5043,7 +5030,7 @@
       <c r="H3" s="7"/>
     </row>
     <row r="4" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="12"/>
@@ -5053,7 +5040,7 @@
       </c>
     </row>
     <row r="5" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="13"/>
@@ -5063,7 +5050,7 @@
       </c>
     </row>
     <row r="6" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="14"/>
@@ -5081,13 +5068,13 @@
       <c r="D8" s="9"/>
     </row>
     <row r="9" spans="1:8" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="6" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="10" t="s">
@@ -5095,21 +5082,21 @@
       </c>
       <c r="E9" s="10"/>
       <c r="F9" s="10"/>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="6" t="s">
         <v>12</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="D9:F9"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B6:D7"/>
+    <mergeCell ref="D9:F9"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.39370078740157483" bottom="0.39370078740157483" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -5125,8 +5112,8 @@
   <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11" style="5" customWidth="1"/>
-    <col min="2" max="2" width="5.625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="11" style="2" customWidth="1"/>
+    <col min="2" max="2" width="5.625" style="2" customWidth="1"/>
     <col min="3" max="3" width="38.875" style="1" customWidth="1"/>
     <col min="4" max="4" width="22.625" style="1" customWidth="1"/>
     <col min="5" max="5" width="11.625" style="1" customWidth="1"/>
@@ -5170,17 +5157,17 @@
       <c r="H3" s="7"/>
     </row>
     <row r="4" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
       <c r="E4" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="13"/>
@@ -5190,7 +5177,7 @@
       </c>
     </row>
     <row r="6" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="14"/>
@@ -5208,13 +5195,13 @@
       <c r="D8" s="9"/>
     </row>
     <row r="9" spans="1:8" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="6" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="10" t="s">
@@ -5222,21 +5209,20 @@
       </c>
       <c r="E9" s="10"/>
       <c r="F9" s="10"/>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="6" t="s">
         <v>12</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="D9:F9"/>
+  <mergeCells count="5">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="B4:C4"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B6:D7"/>
+    <mergeCell ref="D9:F9"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.39370078740157483" bottom="0.39370078740157483" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -5252,8 +5238,8 @@
   <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11" style="5" customWidth="1"/>
-    <col min="2" max="2" width="5.625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="11" style="2" customWidth="1"/>
+    <col min="2" max="2" width="5.625" style="2" customWidth="1"/>
     <col min="3" max="3" width="38.875" style="1" customWidth="1"/>
     <col min="4" max="4" width="22.625" style="1" customWidth="1"/>
     <col min="5" max="5" width="11.625" style="1" customWidth="1"/>
@@ -5297,7 +5283,7 @@
       <c r="H3" s="7"/>
     </row>
     <row r="4" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="12"/>
@@ -5307,7 +5293,7 @@
       </c>
     </row>
     <row r="5" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="13"/>
@@ -5317,7 +5303,7 @@
       </c>
     </row>
     <row r="6" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="14"/>
@@ -5335,13 +5321,13 @@
       <c r="D8" s="9"/>
     </row>
     <row r="9" spans="1:8" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="6" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="10" t="s">
@@ -5349,21 +5335,21 @@
       </c>
       <c r="E9" s="10"/>
       <c r="F9" s="10"/>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="6" t="s">
         <v>12</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="D9:F9"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B6:D7"/>
+    <mergeCell ref="D9:F9"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.39370078740157483" bottom="0.39370078740157483" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -5379,8 +5365,8 @@
   <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11" style="5" customWidth="1"/>
-    <col min="2" max="2" width="5.625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="11" style="2" customWidth="1"/>
+    <col min="2" max="2" width="5.625" style="2" customWidth="1"/>
     <col min="3" max="3" width="38.875" style="1" customWidth="1"/>
     <col min="4" max="4" width="22.625" style="1" customWidth="1"/>
     <col min="5" max="5" width="11.625" style="1" customWidth="1"/>
@@ -5424,7 +5410,7 @@
       <c r="H3" s="7"/>
     </row>
     <row r="4" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="12"/>
@@ -5434,7 +5420,7 @@
       </c>
     </row>
     <row r="5" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="13"/>
@@ -5444,7 +5430,7 @@
       </c>
     </row>
     <row r="6" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="14"/>
@@ -5462,13 +5448,13 @@
       <c r="D8" s="9"/>
     </row>
     <row r="9" spans="1:8" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="6" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="10" t="s">
@@ -5476,21 +5462,21 @@
       </c>
       <c r="E9" s="10"/>
       <c r="F9" s="10"/>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="6" t="s">
         <v>12</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="D9:F9"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B6:D7"/>
+    <mergeCell ref="D9:F9"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.39370078740157483" bottom="0.39370078740157483" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -5506,8 +5492,8 @@
   <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11" style="5" customWidth="1"/>
-    <col min="2" max="2" width="5.625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="11" style="2" customWidth="1"/>
+    <col min="2" max="2" width="5.625" style="2" customWidth="1"/>
     <col min="3" max="3" width="38.875" style="1" customWidth="1"/>
     <col min="4" max="4" width="22.625" style="1" customWidth="1"/>
     <col min="5" max="5" width="11.625" style="1" customWidth="1"/>
@@ -5551,7 +5537,7 @@
       <c r="H3" s="7"/>
     </row>
     <row r="4" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="12"/>
@@ -5561,7 +5547,7 @@
       </c>
     </row>
     <row r="5" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="13"/>
@@ -5571,7 +5557,7 @@
       </c>
     </row>
     <row r="6" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="14"/>
@@ -5589,13 +5575,13 @@
       <c r="D8" s="9"/>
     </row>
     <row r="9" spans="1:8" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="6" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="10" t="s">
@@ -5603,21 +5589,21 @@
       </c>
       <c r="E9" s="10"/>
       <c r="F9" s="10"/>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="6" t="s">
         <v>12</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="D9:F9"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B6:D7"/>
+    <mergeCell ref="D9:F9"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.39370078740157483" bottom="0.39370078740157483" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -5633,8 +5619,8 @@
   <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11" style="5" customWidth="1"/>
-    <col min="2" max="2" width="5.625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="11" style="2" customWidth="1"/>
+    <col min="2" max="2" width="5.625" style="2" customWidth="1"/>
     <col min="3" max="3" width="38.875" style="1" customWidth="1"/>
     <col min="4" max="4" width="22.625" style="1" customWidth="1"/>
     <col min="5" max="5" width="11.625" style="1" customWidth="1"/>
@@ -5678,17 +5664,17 @@
       <c r="H3" s="7"/>
     </row>
     <row r="4" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
       <c r="E4" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="13"/>
@@ -5698,7 +5684,7 @@
       </c>
     </row>
     <row r="6" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="14"/>
@@ -5716,13 +5702,13 @@
       <c r="D8" s="9"/>
     </row>
     <row r="9" spans="1:8" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="6" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="10" t="s">
@@ -5730,21 +5716,20 @@
       </c>
       <c r="E9" s="10"/>
       <c r="F9" s="10"/>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="6" t="s">
         <v>12</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="D9:F9"/>
+  <mergeCells count="5">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="B4:C4"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B6:D7"/>
+    <mergeCell ref="D9:F9"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.39370078740157483" bottom="0.39370078740157483" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -5760,8 +5745,8 @@
   <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11" style="5" customWidth="1"/>
-    <col min="2" max="2" width="5.625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="11" style="2" customWidth="1"/>
+    <col min="2" max="2" width="5.625" style="2" customWidth="1"/>
     <col min="3" max="3" width="38.875" style="1" customWidth="1"/>
     <col min="4" max="4" width="22.625" style="1" customWidth="1"/>
     <col min="5" max="5" width="11.625" style="1" customWidth="1"/>
@@ -5805,17 +5790,17 @@
       <c r="H3" s="7"/>
     </row>
     <row r="4" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
       <c r="E4" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="13"/>
@@ -5825,7 +5810,7 @@
       </c>
     </row>
     <row r="6" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="14"/>
@@ -5843,13 +5828,13 @@
       <c r="D8" s="9"/>
     </row>
     <row r="9" spans="1:8" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="6" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="10" t="s">
@@ -5857,21 +5842,20 @@
       </c>
       <c r="E9" s="10"/>
       <c r="F9" s="10"/>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="6" t="s">
         <v>12</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="D9:F9"/>
+  <mergeCells count="5">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="B4:C4"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B6:D7"/>
+    <mergeCell ref="D9:F9"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.39370078740157483" bottom="0.39370078740157483" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -5887,8 +5871,8 @@
   <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11" style="5" customWidth="1"/>
-    <col min="2" max="2" width="5.625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="11" style="2" customWidth="1"/>
+    <col min="2" max="2" width="5.625" style="2" customWidth="1"/>
     <col min="3" max="3" width="38.875" style="1" customWidth="1"/>
     <col min="4" max="4" width="22.625" style="1" customWidth="1"/>
     <col min="5" max="5" width="11.625" style="1" customWidth="1"/>
@@ -5932,17 +5916,17 @@
       <c r="H3" s="7"/>
     </row>
     <row r="4" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
       <c r="E4" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="13"/>
@@ -5952,7 +5936,7 @@
       </c>
     </row>
     <row r="6" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="14"/>
@@ -5970,13 +5954,13 @@
       <c r="D8" s="9"/>
     </row>
     <row r="9" spans="1:8" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="6" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="10" t="s">
@@ -5984,21 +5968,20 @@
       </c>
       <c r="E9" s="10"/>
       <c r="F9" s="10"/>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="6" t="s">
         <v>12</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="D9:F9"/>
+  <mergeCells count="5">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="B4:C4"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B6:D7"/>
+    <mergeCell ref="D9:F9"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.39370078740157483" bottom="0.39370078740157483" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -6014,8 +5997,8 @@
   <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11" style="5" customWidth="1"/>
-    <col min="2" max="2" width="5.625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="11" style="2" customWidth="1"/>
+    <col min="2" max="2" width="5.625" style="2" customWidth="1"/>
     <col min="3" max="3" width="38.875" style="1" customWidth="1"/>
     <col min="4" max="4" width="22.625" style="1" customWidth="1"/>
     <col min="5" max="5" width="11.625" style="1" customWidth="1"/>
@@ -6059,17 +6042,17 @@
       <c r="H3" s="7"/>
     </row>
     <row r="4" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
       <c r="E4" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="13"/>
@@ -6079,7 +6062,7 @@
       </c>
     </row>
     <row r="6" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="14"/>
@@ -6097,13 +6080,13 @@
       <c r="D8" s="9"/>
     </row>
     <row r="9" spans="1:8" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="6" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="10" t="s">
@@ -6111,21 +6094,20 @@
       </c>
       <c r="E9" s="10"/>
       <c r="F9" s="10"/>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="6" t="s">
         <v>12</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="D9:F9"/>
+  <mergeCells count="5">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="B4:C4"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B6:D7"/>
+    <mergeCell ref="D9:F9"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.39370078740157483" bottom="0.39370078740157483" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -6141,8 +6123,8 @@
   <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11" style="5" customWidth="1"/>
-    <col min="2" max="2" width="5.625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="11" style="2" customWidth="1"/>
+    <col min="2" max="2" width="5.625" style="2" customWidth="1"/>
     <col min="3" max="3" width="38.875" style="1" customWidth="1"/>
     <col min="4" max="4" width="22.625" style="1" customWidth="1"/>
     <col min="5" max="5" width="11.625" style="1" customWidth="1"/>
@@ -6186,7 +6168,7 @@
       <c r="H3" s="7"/>
     </row>
     <row r="4" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="12"/>
@@ -6196,7 +6178,7 @@
       </c>
     </row>
     <row r="5" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="13"/>
@@ -6206,7 +6188,7 @@
       </c>
     </row>
     <row r="6" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="14"/>
@@ -6224,13 +6206,13 @@
       <c r="D8" s="9"/>
     </row>
     <row r="9" spans="1:8" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="6" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="10" t="s">
@@ -6238,21 +6220,21 @@
       </c>
       <c r="E9" s="10"/>
       <c r="F9" s="10"/>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="6" t="s">
         <v>12</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="D9:F9"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B6:D7"/>
+    <mergeCell ref="D9:F9"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.39370078740157483" bottom="0.39370078740157483" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -6268,8 +6250,8 @@
   <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11" style="5" customWidth="1"/>
-    <col min="2" max="2" width="5.625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="11" style="2" customWidth="1"/>
+    <col min="2" max="2" width="5.625" style="2" customWidth="1"/>
     <col min="3" max="3" width="38.875" style="1" customWidth="1"/>
     <col min="4" max="4" width="22.625" style="1" customWidth="1"/>
     <col min="5" max="5" width="11.625" style="1" customWidth="1"/>
@@ -6313,7 +6295,7 @@
       <c r="H3" s="7"/>
     </row>
     <row r="4" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="12"/>
@@ -6323,7 +6305,7 @@
       </c>
     </row>
     <row r="5" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="13"/>
@@ -6333,7 +6315,7 @@
       </c>
     </row>
     <row r="6" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="14"/>
@@ -6351,13 +6333,13 @@
       <c r="D8" s="9"/>
     </row>
     <row r="9" spans="1:8" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="6" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="10" t="s">
@@ -6365,21 +6347,21 @@
       </c>
       <c r="E9" s="10"/>
       <c r="F9" s="10"/>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="6" t="s">
         <v>12</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="D9:F9"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B6:D7"/>
+    <mergeCell ref="D9:F9"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.39370078740157483" bottom="0.39370078740157483" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -6395,8 +6377,8 @@
   <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11" style="5" customWidth="1"/>
-    <col min="2" max="2" width="5.625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="11" style="2" customWidth="1"/>
+    <col min="2" max="2" width="5.625" style="2" customWidth="1"/>
     <col min="3" max="3" width="38.875" style="1" customWidth="1"/>
     <col min="4" max="4" width="22.625" style="1" customWidth="1"/>
     <col min="5" max="5" width="11.625" style="1" customWidth="1"/>
@@ -6440,7 +6422,7 @@
       <c r="H3" s="7"/>
     </row>
     <row r="4" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="12"/>
@@ -6450,7 +6432,7 @@
       </c>
     </row>
     <row r="5" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="13"/>
@@ -6460,7 +6442,7 @@
       </c>
     </row>
     <row r="6" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="14"/>
@@ -6478,13 +6460,13 @@
       <c r="D8" s="9"/>
     </row>
     <row r="9" spans="1:8" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="6" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="10" t="s">
@@ -6492,21 +6474,21 @@
       </c>
       <c r="E9" s="10"/>
       <c r="F9" s="10"/>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="6" t="s">
         <v>12</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="D9:F9"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B6:D7"/>
+    <mergeCell ref="D9:F9"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.39370078740157483" bottom="0.39370078740157483" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -6522,8 +6504,8 @@
   <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11" style="5" customWidth="1"/>
-    <col min="2" max="2" width="5.625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="11" style="2" customWidth="1"/>
+    <col min="2" max="2" width="5.625" style="2" customWidth="1"/>
     <col min="3" max="3" width="38.875" style="1" customWidth="1"/>
     <col min="4" max="4" width="22.625" style="1" customWidth="1"/>
     <col min="5" max="5" width="11.625" style="1" customWidth="1"/>
@@ -6567,17 +6549,17 @@
       <c r="H3" s="7"/>
     </row>
     <row r="4" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
       <c r="E4" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="13"/>
@@ -6587,7 +6569,7 @@
       </c>
     </row>
     <row r="6" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="14"/>
@@ -6605,13 +6587,13 @@
       <c r="D8" s="9"/>
     </row>
     <row r="9" spans="1:8" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="6" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="10" t="s">
@@ -6619,21 +6601,20 @@
       </c>
       <c r="E9" s="10"/>
       <c r="F9" s="10"/>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="6" t="s">
         <v>12</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="D9:F9"/>
+  <mergeCells count="5">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="B4:C4"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B6:D7"/>
+    <mergeCell ref="D9:F9"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.39370078740157483" bottom="0.39370078740157483" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -6649,8 +6630,8 @@
   <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11" style="5" customWidth="1"/>
-    <col min="2" max="2" width="5.625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="11" style="2" customWidth="1"/>
+    <col min="2" max="2" width="5.625" style="2" customWidth="1"/>
     <col min="3" max="3" width="38.875" style="1" customWidth="1"/>
     <col min="4" max="4" width="22.625" style="1" customWidth="1"/>
     <col min="5" max="5" width="11.625" style="1" customWidth="1"/>
@@ -6694,7 +6675,7 @@
       <c r="H3" s="7"/>
     </row>
     <row r="4" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="12"/>
@@ -6704,7 +6685,7 @@
       </c>
     </row>
     <row r="5" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="13"/>
@@ -6714,7 +6695,7 @@
       </c>
     </row>
     <row r="6" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="14"/>
@@ -6732,13 +6713,13 @@
       <c r="D8" s="9"/>
     </row>
     <row r="9" spans="1:8" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="6" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="10" t="s">
@@ -6746,21 +6727,21 @@
       </c>
       <c r="E9" s="10"/>
       <c r="F9" s="10"/>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="6" t="s">
         <v>12</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="D9:F9"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B6:D7"/>
+    <mergeCell ref="D9:F9"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.39370078740157483" bottom="0.39370078740157483" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -6776,8 +6757,8 @@
   <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11" style="5" customWidth="1"/>
-    <col min="2" max="2" width="5.625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="11" style="2" customWidth="1"/>
+    <col min="2" max="2" width="5.625" style="2" customWidth="1"/>
     <col min="3" max="3" width="38.875" style="1" customWidth="1"/>
     <col min="4" max="4" width="22.625" style="1" customWidth="1"/>
     <col min="5" max="5" width="11.625" style="1" customWidth="1"/>
@@ -6821,7 +6802,7 @@
       <c r="H3" s="7"/>
     </row>
     <row r="4" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="12"/>
@@ -6831,7 +6812,7 @@
       </c>
     </row>
     <row r="5" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="13"/>
@@ -6841,7 +6822,7 @@
       </c>
     </row>
     <row r="6" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="14"/>
@@ -6859,13 +6840,13 @@
       <c r="D8" s="9"/>
     </row>
     <row r="9" spans="1:8" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="6" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="10" t="s">
@@ -6873,21 +6854,21 @@
       </c>
       <c r="E9" s="10"/>
       <c r="F9" s="10"/>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="6" t="s">
         <v>12</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="D9:F9"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B6:D7"/>
+    <mergeCell ref="D9:F9"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.39370078740157483" bottom="0.39370078740157483" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -6903,8 +6884,8 @@
   <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11" style="5" customWidth="1"/>
-    <col min="2" max="2" width="5.625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="11" style="2" customWidth="1"/>
+    <col min="2" max="2" width="5.625" style="2" customWidth="1"/>
     <col min="3" max="3" width="38.875" style="1" customWidth="1"/>
     <col min="4" max="4" width="22.625" style="1" customWidth="1"/>
     <col min="5" max="5" width="11.625" style="1" customWidth="1"/>
@@ -6948,7 +6929,7 @@
       <c r="H3" s="7"/>
     </row>
     <row r="4" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="12"/>
@@ -6958,7 +6939,7 @@
       </c>
     </row>
     <row r="5" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="13"/>
@@ -6968,7 +6949,7 @@
       </c>
     </row>
     <row r="6" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="14"/>
@@ -6986,13 +6967,13 @@
       <c r="D8" s="9"/>
     </row>
     <row r="9" spans="1:8" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="6" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="10" t="s">
@@ -7000,21 +6981,21 @@
       </c>
       <c r="E9" s="10"/>
       <c r="F9" s="10"/>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="6" t="s">
         <v>12</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="D9:F9"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B6:D7"/>
+    <mergeCell ref="D9:F9"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.39370078740157483" bottom="0.39370078740157483" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -7030,8 +7011,8 @@
   <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11" style="5" customWidth="1"/>
-    <col min="2" max="2" width="5.625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="11" style="2" customWidth="1"/>
+    <col min="2" max="2" width="5.625" style="2" customWidth="1"/>
     <col min="3" max="3" width="38.875" style="1" customWidth="1"/>
     <col min="4" max="4" width="22.625" style="1" customWidth="1"/>
     <col min="5" max="5" width="11.625" style="1" customWidth="1"/>
@@ -7075,17 +7056,17 @@
       <c r="H3" s="7"/>
     </row>
     <row r="4" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
       <c r="E4" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="13"/>
@@ -7095,7 +7076,7 @@
       </c>
     </row>
     <row r="6" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="14"/>
@@ -7113,13 +7094,13 @@
       <c r="D8" s="9"/>
     </row>
     <row r="9" spans="1:8" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="6" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="10" t="s">
@@ -7127,21 +7108,20 @@
       </c>
       <c r="E9" s="10"/>
       <c r="F9" s="10"/>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="6" t="s">
         <v>12</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="D9:F9"/>
+  <mergeCells count="5">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="B4:C4"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B6:D7"/>
+    <mergeCell ref="D9:F9"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.39370078740157483" bottom="0.39370078740157483" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -7157,8 +7137,8 @@
   <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11" style="5" customWidth="1"/>
-    <col min="2" max="2" width="5.625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="11" style="2" customWidth="1"/>
+    <col min="2" max="2" width="5.625" style="2" customWidth="1"/>
     <col min="3" max="3" width="38.875" style="1" customWidth="1"/>
     <col min="4" max="4" width="22.625" style="1" customWidth="1"/>
     <col min="5" max="5" width="11.625" style="1" customWidth="1"/>
@@ -7202,17 +7182,17 @@
       <c r="H3" s="7"/>
     </row>
     <row r="4" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
       <c r="E4" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="13"/>
@@ -7222,7 +7202,7 @@
       </c>
     </row>
     <row r="6" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="14"/>
@@ -7240,13 +7220,13 @@
       <c r="D8" s="9"/>
     </row>
     <row r="9" spans="1:8" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="6" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="10" t="s">
@@ -7254,21 +7234,20 @@
       </c>
       <c r="E9" s="10"/>
       <c r="F9" s="10"/>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="6" t="s">
         <v>12</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="D9:F9"/>
+  <mergeCells count="5">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="B4:C4"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B6:D7"/>
+    <mergeCell ref="D9:F9"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.39370078740157483" bottom="0.39370078740157483" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -7284,8 +7263,8 @@
   <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11" style="5" customWidth="1"/>
-    <col min="2" max="2" width="5.625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="11" style="2" customWidth="1"/>
+    <col min="2" max="2" width="5.625" style="2" customWidth="1"/>
     <col min="3" max="3" width="38.875" style="1" customWidth="1"/>
     <col min="4" max="4" width="22.625" style="1" customWidth="1"/>
     <col min="5" max="5" width="11.625" style="1" customWidth="1"/>
@@ -7329,17 +7308,17 @@
       <c r="H3" s="7"/>
     </row>
     <row r="4" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
       <c r="E4" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="13"/>
@@ -7349,7 +7328,7 @@
       </c>
     </row>
     <row r="6" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="14"/>
@@ -7367,13 +7346,13 @@
       <c r="D8" s="9"/>
     </row>
     <row r="9" spans="1:8" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="6" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="10" t="s">
@@ -7381,21 +7360,20 @@
       </c>
       <c r="E9" s="10"/>
       <c r="F9" s="10"/>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="6" t="s">
         <v>12</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="D9:F9"/>
+  <mergeCells count="5">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="B4:C4"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B6:D7"/>
+    <mergeCell ref="D9:F9"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.39370078740157483" bottom="0.39370078740157483" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -7411,8 +7389,8 @@
   <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11" style="5" customWidth="1"/>
-    <col min="2" max="2" width="5.625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="11" style="2" customWidth="1"/>
+    <col min="2" max="2" width="5.625" style="2" customWidth="1"/>
     <col min="3" max="3" width="38.875" style="1" customWidth="1"/>
     <col min="4" max="4" width="22.625" style="1" customWidth="1"/>
     <col min="5" max="5" width="11.625" style="1" customWidth="1"/>
@@ -7456,17 +7434,17 @@
       <c r="H3" s="7"/>
     </row>
     <row r="4" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
       <c r="E4" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="13"/>
@@ -7476,7 +7454,7 @@
       </c>
     </row>
     <row r="6" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="14"/>
@@ -7494,13 +7472,13 @@
       <c r="D8" s="9"/>
     </row>
     <row r="9" spans="1:8" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="6" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="10" t="s">
@@ -7508,21 +7486,20 @@
       </c>
       <c r="E9" s="10"/>
       <c r="F9" s="10"/>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="6" t="s">
         <v>12</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="D9:F9"/>
+  <mergeCells count="5">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="B4:C4"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B6:D7"/>
+    <mergeCell ref="D9:F9"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.39370078740157483" bottom="0.39370078740157483" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -7538,8 +7515,8 @@
   <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11" style="5" customWidth="1"/>
-    <col min="2" max="2" width="5.625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="11" style="2" customWidth="1"/>
+    <col min="2" max="2" width="5.625" style="2" customWidth="1"/>
     <col min="3" max="3" width="38.875" style="1" customWidth="1"/>
     <col min="4" max="4" width="22.625" style="1" customWidth="1"/>
     <col min="5" max="5" width="11.625" style="1" customWidth="1"/>
@@ -7583,7 +7560,7 @@
       <c r="H3" s="7"/>
     </row>
     <row r="4" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="12"/>
@@ -7593,7 +7570,7 @@
       </c>
     </row>
     <row r="5" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="13"/>
@@ -7603,7 +7580,7 @@
       </c>
     </row>
     <row r="6" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="14"/>
@@ -7621,13 +7598,13 @@
       <c r="D8" s="9"/>
     </row>
     <row r="9" spans="1:8" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="6" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="10" t="s">
@@ -7635,21 +7612,21 @@
       </c>
       <c r="E9" s="10"/>
       <c r="F9" s="10"/>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="6" t="s">
         <v>12</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="D9:F9"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B6:D7"/>
+    <mergeCell ref="D9:F9"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.39370078740157483" bottom="0.39370078740157483" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -7665,8 +7642,8 @@
   <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11" style="5" customWidth="1"/>
-    <col min="2" max="2" width="5.625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="11" style="2" customWidth="1"/>
+    <col min="2" max="2" width="5.625" style="2" customWidth="1"/>
     <col min="3" max="3" width="38.875" style="1" customWidth="1"/>
     <col min="4" max="4" width="22.625" style="1" customWidth="1"/>
     <col min="5" max="5" width="11.625" style="1" customWidth="1"/>
@@ -7710,7 +7687,7 @@
       <c r="H3" s="7"/>
     </row>
     <row r="4" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="12"/>
@@ -7720,7 +7697,7 @@
       </c>
     </row>
     <row r="5" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="13"/>
@@ -7730,7 +7707,7 @@
       </c>
     </row>
     <row r="6" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="14"/>
@@ -7748,13 +7725,13 @@
       <c r="D8" s="9"/>
     </row>
     <row r="9" spans="1:8" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="6" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="10" t="s">
@@ -7762,21 +7739,21 @@
       </c>
       <c r="E9" s="10"/>
       <c r="F9" s="10"/>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="6" t="s">
         <v>12</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="D9:F9"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B6:D7"/>
+    <mergeCell ref="D9:F9"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.39370078740157483" bottom="0.39370078740157483" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -7792,8 +7769,8 @@
   <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11" style="5" customWidth="1"/>
-    <col min="2" max="2" width="5.625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="11" style="2" customWidth="1"/>
+    <col min="2" max="2" width="5.625" style="2" customWidth="1"/>
     <col min="3" max="3" width="38.875" style="1" customWidth="1"/>
     <col min="4" max="4" width="22.625" style="1" customWidth="1"/>
     <col min="5" max="5" width="11.625" style="1" customWidth="1"/>
@@ -7837,7 +7814,7 @@
       <c r="H3" s="7"/>
     </row>
     <row r="4" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="12"/>
@@ -7847,7 +7824,7 @@
       </c>
     </row>
     <row r="5" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="13"/>
@@ -7857,7 +7834,7 @@
       </c>
     </row>
     <row r="6" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="14"/>
@@ -7875,13 +7852,13 @@
       <c r="D8" s="9"/>
     </row>
     <row r="9" spans="1:8" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="6" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="10" t="s">
@@ -7889,21 +7866,21 @@
       </c>
       <c r="E9" s="10"/>
       <c r="F9" s="10"/>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="6" t="s">
         <v>12</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="D9:F9"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B6:D7"/>
+    <mergeCell ref="D9:F9"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.39370078740157483" bottom="0.39370078740157483" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -7919,8 +7896,8 @@
   <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11" style="5" customWidth="1"/>
-    <col min="2" max="2" width="5.625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="11" style="2" customWidth="1"/>
+    <col min="2" max="2" width="5.625" style="2" customWidth="1"/>
     <col min="3" max="3" width="38.875" style="1" customWidth="1"/>
     <col min="4" max="4" width="22.625" style="1" customWidth="1"/>
     <col min="5" max="5" width="11.625" style="1" customWidth="1"/>
@@ -7964,17 +7941,17 @@
       <c r="H3" s="7"/>
     </row>
     <row r="4" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
       <c r="E4" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="13"/>
@@ -7984,7 +7961,7 @@
       </c>
     </row>
     <row r="6" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="14"/>
@@ -8002,13 +7979,13 @@
       <c r="D8" s="9"/>
     </row>
     <row r="9" spans="1:8" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="6" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="10" t="s">
@@ -8016,21 +7993,20 @@
       </c>
       <c r="E9" s="10"/>
       <c r="F9" s="10"/>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="6" t="s">
         <v>12</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="D9:F9"/>
+  <mergeCells count="5">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="B4:C4"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B6:D7"/>
+    <mergeCell ref="D9:F9"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.39370078740157483" bottom="0.39370078740157483" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -8046,8 +8022,8 @@
   <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11" style="5" customWidth="1"/>
-    <col min="2" max="2" width="5.625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="11" style="2" customWidth="1"/>
+    <col min="2" max="2" width="5.625" style="2" customWidth="1"/>
     <col min="3" max="3" width="38.875" style="1" customWidth="1"/>
     <col min="4" max="4" width="22.625" style="1" customWidth="1"/>
     <col min="5" max="5" width="11.625" style="1" customWidth="1"/>
@@ -8091,7 +8067,7 @@
       <c r="H3" s="7"/>
     </row>
     <row r="4" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="12"/>
@@ -8101,7 +8077,7 @@
       </c>
     </row>
     <row r="5" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="13"/>
@@ -8111,7 +8087,7 @@
       </c>
     </row>
     <row r="6" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="14"/>
@@ -8129,13 +8105,13 @@
       <c r="D8" s="9"/>
     </row>
     <row r="9" spans="1:8" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="6" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="10" t="s">
@@ -8143,21 +8119,21 @@
       </c>
       <c r="E9" s="10"/>
       <c r="F9" s="10"/>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="6" t="s">
         <v>12</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="D9:F9"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B6:D7"/>
+    <mergeCell ref="D9:F9"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.39370078740157483" bottom="0.39370078740157483" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -8173,8 +8149,8 @@
   <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11" style="5" customWidth="1"/>
-    <col min="2" max="2" width="5.625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="11" style="2" customWidth="1"/>
+    <col min="2" max="2" width="5.625" style="2" customWidth="1"/>
     <col min="3" max="3" width="38.875" style="1" customWidth="1"/>
     <col min="4" max="4" width="22.625" style="1" customWidth="1"/>
     <col min="5" max="5" width="11.625" style="1" customWidth="1"/>
@@ -8218,7 +8194,7 @@
       <c r="H3" s="7"/>
     </row>
     <row r="4" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="12"/>
@@ -8228,7 +8204,7 @@
       </c>
     </row>
     <row r="5" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="13"/>
@@ -8238,7 +8214,7 @@
       </c>
     </row>
     <row r="6" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="14"/>
@@ -8256,13 +8232,13 @@
       <c r="D8" s="9"/>
     </row>
     <row r="9" spans="1:8" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="6" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="10" t="s">
@@ -8270,21 +8246,21 @@
       </c>
       <c r="E9" s="10"/>
       <c r="F9" s="10"/>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="6" t="s">
         <v>12</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="D9:F9"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B6:D7"/>
+    <mergeCell ref="D9:F9"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.39370078740157483" bottom="0.39370078740157483" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -8300,8 +8276,8 @@
   <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11" style="5" customWidth="1"/>
-    <col min="2" max="2" width="5.625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="11" style="2" customWidth="1"/>
+    <col min="2" max="2" width="5.625" style="2" customWidth="1"/>
     <col min="3" max="3" width="38.875" style="1" customWidth="1"/>
     <col min="4" max="4" width="22.625" style="1" customWidth="1"/>
     <col min="5" max="5" width="11.625" style="1" customWidth="1"/>
@@ -8345,7 +8321,7 @@
       <c r="H3" s="7"/>
     </row>
     <row r="4" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="12"/>
@@ -8355,7 +8331,7 @@
       </c>
     </row>
     <row r="5" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="13"/>
@@ -8365,7 +8341,7 @@
       </c>
     </row>
     <row r="6" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="14"/>
@@ -8383,13 +8359,13 @@
       <c r="D8" s="9"/>
     </row>
     <row r="9" spans="1:8" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="6" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="10" t="s">
@@ -8397,21 +8373,21 @@
       </c>
       <c r="E9" s="10"/>
       <c r="F9" s="10"/>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="6" t="s">
         <v>12</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="D9:F9"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B6:D7"/>
+    <mergeCell ref="D9:F9"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.39370078740157483" bottom="0.39370078740157483" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -8427,8 +8403,8 @@
   <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11" style="5" customWidth="1"/>
-    <col min="2" max="2" width="5.625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="11" style="2" customWidth="1"/>
+    <col min="2" max="2" width="5.625" style="2" customWidth="1"/>
     <col min="3" max="3" width="38.875" style="1" customWidth="1"/>
     <col min="4" max="4" width="22.625" style="1" customWidth="1"/>
     <col min="5" max="5" width="11.625" style="1" customWidth="1"/>
@@ -8472,17 +8448,17 @@
       <c r="H3" s="7"/>
     </row>
     <row r="4" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
       <c r="E4" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="13"/>
@@ -8492,7 +8468,7 @@
       </c>
     </row>
     <row r="6" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="14"/>
@@ -8510,13 +8486,13 @@
       <c r="D8" s="9"/>
     </row>
     <row r="9" spans="1:8" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="6" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="10" t="s">
@@ -8524,21 +8500,20 @@
       </c>
       <c r="E9" s="10"/>
       <c r="F9" s="10"/>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="6" t="s">
         <v>12</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="D9:F9"/>
+  <mergeCells count="5">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="B4:C4"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B6:D7"/>
+    <mergeCell ref="D9:F9"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.39370078740157483" bottom="0.39370078740157483" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -8554,8 +8529,8 @@
   <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11" style="5" customWidth="1"/>
-    <col min="2" max="2" width="5.625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="11" style="2" customWidth="1"/>
+    <col min="2" max="2" width="5.625" style="2" customWidth="1"/>
     <col min="3" max="3" width="38.875" style="1" customWidth="1"/>
     <col min="4" max="4" width="22.625" style="1" customWidth="1"/>
     <col min="5" max="5" width="11.625" style="1" customWidth="1"/>
@@ -8599,17 +8574,17 @@
       <c r="H3" s="7"/>
     </row>
     <row r="4" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
       <c r="E4" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="13"/>
@@ -8619,7 +8594,7 @@
       </c>
     </row>
     <row r="6" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="14"/>
@@ -8637,13 +8612,13 @@
       <c r="D8" s="9"/>
     </row>
     <row r="9" spans="1:8" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="6" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="10" t="s">
@@ -8651,21 +8626,20 @@
       </c>
       <c r="E9" s="10"/>
       <c r="F9" s="10"/>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="6" t="s">
         <v>12</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="D9:F9"/>
+  <mergeCells count="5">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="B4:C4"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B6:D7"/>
+    <mergeCell ref="D9:F9"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.39370078740157483" bottom="0.39370078740157483" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -8681,8 +8655,8 @@
   <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11" style="5" customWidth="1"/>
-    <col min="2" max="2" width="5.625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="11" style="2" customWidth="1"/>
+    <col min="2" max="2" width="5.625" style="2" customWidth="1"/>
     <col min="3" max="3" width="38.875" style="1" customWidth="1"/>
     <col min="4" max="4" width="22.625" style="1" customWidth="1"/>
     <col min="5" max="5" width="11.625" style="1" customWidth="1"/>
@@ -8726,17 +8700,17 @@
       <c r="H3" s="7"/>
     </row>
     <row r="4" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
       <c r="E4" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="13"/>
@@ -8746,7 +8720,7 @@
       </c>
     </row>
     <row r="6" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="14"/>
@@ -8764,13 +8738,13 @@
       <c r="D8" s="9"/>
     </row>
     <row r="9" spans="1:8" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="6" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="10" t="s">
@@ -8778,21 +8752,20 @@
       </c>
       <c r="E9" s="10"/>
       <c r="F9" s="10"/>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="6" t="s">
         <v>12</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="D9:F9"/>
+  <mergeCells count="5">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="B4:C4"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B6:D7"/>
+    <mergeCell ref="D9:F9"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.39370078740157483" bottom="0.39370078740157483" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -8808,8 +8781,8 @@
   <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11" style="5" customWidth="1"/>
-    <col min="2" max="2" width="5.625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="11" style="2" customWidth="1"/>
+    <col min="2" max="2" width="5.625" style="2" customWidth="1"/>
     <col min="3" max="3" width="38.875" style="1" customWidth="1"/>
     <col min="4" max="4" width="22.625" style="1" customWidth="1"/>
     <col min="5" max="5" width="11.625" style="1" customWidth="1"/>
@@ -8853,17 +8826,17 @@
       <c r="H3" s="7"/>
     </row>
     <row r="4" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
       <c r="E4" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="13"/>
@@ -8873,7 +8846,7 @@
       </c>
     </row>
     <row r="6" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="14"/>
@@ -8891,13 +8864,13 @@
       <c r="D8" s="9"/>
     </row>
     <row r="9" spans="1:8" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="6" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="10" t="s">
@@ -8905,21 +8878,20 @@
       </c>
       <c r="E9" s="10"/>
       <c r="F9" s="10"/>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="6" t="s">
         <v>12</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="D9:F9"/>
+  <mergeCells count="5">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="B4:C4"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B6:D7"/>
+    <mergeCell ref="D9:F9"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.39370078740157483" bottom="0.39370078740157483" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -8935,8 +8907,8 @@
   <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11" style="5" customWidth="1"/>
-    <col min="2" max="2" width="5.625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="11" style="2" customWidth="1"/>
+    <col min="2" max="2" width="5.625" style="2" customWidth="1"/>
     <col min="3" max="3" width="38.875" style="1" customWidth="1"/>
     <col min="4" max="4" width="22.625" style="1" customWidth="1"/>
     <col min="5" max="5" width="11.625" style="1" customWidth="1"/>
@@ -8980,7 +8952,7 @@
       <c r="H3" s="7"/>
     </row>
     <row r="4" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="12"/>
@@ -8990,7 +8962,7 @@
       </c>
     </row>
     <row r="5" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="13"/>
@@ -9000,7 +8972,7 @@
       </c>
     </row>
     <row r="6" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="14"/>
@@ -9018,13 +8990,13 @@
       <c r="D8" s="9"/>
     </row>
     <row r="9" spans="1:8" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="6" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="10" t="s">
@@ -9032,21 +9004,21 @@
       </c>
       <c r="E9" s="10"/>
       <c r="F9" s="10"/>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="6" t="s">
         <v>12</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="D9:F9"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B6:D7"/>
+    <mergeCell ref="D9:F9"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.39370078740157483" bottom="0.39370078740157483" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -9062,8 +9034,8 @@
   <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11" style="5" customWidth="1"/>
-    <col min="2" max="2" width="5.625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="11" style="2" customWidth="1"/>
+    <col min="2" max="2" width="5.625" style="2" customWidth="1"/>
     <col min="3" max="3" width="38.875" style="1" customWidth="1"/>
     <col min="4" max="4" width="22.625" style="1" customWidth="1"/>
     <col min="5" max="5" width="11.625" style="1" customWidth="1"/>
@@ -9107,7 +9079,7 @@
       <c r="H3" s="7"/>
     </row>
     <row r="4" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="12"/>
@@ -9117,7 +9089,7 @@
       </c>
     </row>
     <row r="5" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="13"/>
@@ -9127,7 +9099,7 @@
       </c>
     </row>
     <row r="6" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="14"/>
@@ -9145,13 +9117,13 @@
       <c r="D8" s="9"/>
     </row>
     <row r="9" spans="1:8" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="6" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="10" t="s">
@@ -9159,21 +9131,21 @@
       </c>
       <c r="E9" s="10"/>
       <c r="F9" s="10"/>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="6" t="s">
         <v>12</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="D9:F9"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B6:D7"/>
+    <mergeCell ref="D9:F9"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.39370078740157483" bottom="0.39370078740157483" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -9189,8 +9161,8 @@
   <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11" style="5" customWidth="1"/>
-    <col min="2" max="2" width="5.625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="11" style="2" customWidth="1"/>
+    <col min="2" max="2" width="5.625" style="2" customWidth="1"/>
     <col min="3" max="3" width="38.875" style="1" customWidth="1"/>
     <col min="4" max="4" width="22.625" style="1" customWidth="1"/>
     <col min="5" max="5" width="11.625" style="1" customWidth="1"/>
@@ -9234,7 +9206,7 @@
       <c r="H3" s="7"/>
     </row>
     <row r="4" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="12"/>
@@ -9244,7 +9216,7 @@
       </c>
     </row>
     <row r="5" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="13"/>
@@ -9254,7 +9226,7 @@
       </c>
     </row>
     <row r="6" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="14"/>
@@ -9272,13 +9244,13 @@
       <c r="D8" s="9"/>
     </row>
     <row r="9" spans="1:8" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="6" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="10" t="s">
@@ -9286,21 +9258,21 @@
       </c>
       <c r="E9" s="10"/>
       <c r="F9" s="10"/>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="6" t="s">
         <v>12</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="D9:F9"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B6:D7"/>
+    <mergeCell ref="D9:F9"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.39370078740157483" bottom="0.39370078740157483" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -9316,8 +9288,8 @@
   <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11" style="5" customWidth="1"/>
-    <col min="2" max="2" width="5.625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="11" style="2" customWidth="1"/>
+    <col min="2" max="2" width="5.625" style="2" customWidth="1"/>
     <col min="3" max="3" width="38.875" style="1" customWidth="1"/>
     <col min="4" max="4" width="22.625" style="1" customWidth="1"/>
     <col min="5" max="5" width="11.625" style="1" customWidth="1"/>
@@ -9361,7 +9333,7 @@
       <c r="H3" s="7"/>
     </row>
     <row r="4" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="12"/>
@@ -9371,7 +9343,7 @@
       </c>
     </row>
     <row r="5" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="13"/>
@@ -9381,7 +9353,7 @@
       </c>
     </row>
     <row r="6" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="14"/>
@@ -9399,13 +9371,13 @@
       <c r="D8" s="9"/>
     </row>
     <row r="9" spans="1:8" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="6" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="10" t="s">
@@ -9413,21 +9385,21 @@
       </c>
       <c r="E9" s="10"/>
       <c r="F9" s="10"/>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="6" t="s">
         <v>12</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="D9:F9"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B6:D7"/>
+    <mergeCell ref="D9:F9"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.39370078740157483" bottom="0.39370078740157483" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -9443,8 +9415,8 @@
   <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11" style="5" customWidth="1"/>
-    <col min="2" max="2" width="5.625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="11" style="2" customWidth="1"/>
+    <col min="2" max="2" width="5.625" style="2" customWidth="1"/>
     <col min="3" max="3" width="38.875" style="1" customWidth="1"/>
     <col min="4" max="4" width="22.625" style="1" customWidth="1"/>
     <col min="5" max="5" width="11.625" style="1" customWidth="1"/>
@@ -9488,7 +9460,7 @@
       <c r="H3" s="7"/>
     </row>
     <row r="4" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="12"/>
@@ -9498,7 +9470,7 @@
       </c>
     </row>
     <row r="5" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="13"/>
@@ -9508,7 +9480,7 @@
       </c>
     </row>
     <row r="6" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="14"/>
@@ -9526,13 +9498,13 @@
       <c r="D8" s="9"/>
     </row>
     <row r="9" spans="1:8" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="6" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="10" t="s">
@@ -9540,21 +9512,21 @@
       </c>
       <c r="E9" s="10"/>
       <c r="F9" s="10"/>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="6" t="s">
         <v>12</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="D9:F9"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B6:D7"/>
+    <mergeCell ref="D9:F9"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.39370078740157483" bottom="0.39370078740157483" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -9570,8 +9542,8 @@
   <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11" style="5" customWidth="1"/>
-    <col min="2" max="2" width="5.625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="11" style="2" customWidth="1"/>
+    <col min="2" max="2" width="5.625" style="2" customWidth="1"/>
     <col min="3" max="3" width="38.875" style="1" customWidth="1"/>
     <col min="4" max="4" width="22.625" style="1" customWidth="1"/>
     <col min="5" max="5" width="11.625" style="1" customWidth="1"/>
@@ -9615,7 +9587,7 @@
       <c r="H3" s="7"/>
     </row>
     <row r="4" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="12"/>
@@ -9625,7 +9597,7 @@
       </c>
     </row>
     <row r="5" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="13"/>
@@ -9635,7 +9607,7 @@
       </c>
     </row>
     <row r="6" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="14"/>
@@ -9653,13 +9625,13 @@
       <c r="D8" s="9"/>
     </row>
     <row r="9" spans="1:8" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="6" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="10" t="s">
@@ -9667,21 +9639,21 @@
       </c>
       <c r="E9" s="10"/>
       <c r="F9" s="10"/>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="6" t="s">
         <v>12</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="D9:F9"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B6:D7"/>
+    <mergeCell ref="D9:F9"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.39370078740157483" bottom="0.39370078740157483" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -9697,8 +9669,8 @@
   <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11" style="5" customWidth="1"/>
-    <col min="2" max="2" width="5.625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="11" style="2" customWidth="1"/>
+    <col min="2" max="2" width="5.625" style="2" customWidth="1"/>
     <col min="3" max="3" width="38.875" style="1" customWidth="1"/>
     <col min="4" max="4" width="22.625" style="1" customWidth="1"/>
     <col min="5" max="5" width="11.625" style="1" customWidth="1"/>
@@ -9742,7 +9714,7 @@
       <c r="H3" s="7"/>
     </row>
     <row r="4" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="12"/>
@@ -9752,7 +9724,7 @@
       </c>
     </row>
     <row r="5" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="13"/>
@@ -9762,7 +9734,7 @@
       </c>
     </row>
     <row r="6" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="14"/>
@@ -9780,13 +9752,13 @@
       <c r="D8" s="9"/>
     </row>
     <row r="9" spans="1:8" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="6" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="10" t="s">
@@ -9794,21 +9766,21 @@
       </c>
       <c r="E9" s="10"/>
       <c r="F9" s="10"/>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="6" t="s">
         <v>12</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="D9:F9"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B6:D7"/>
+    <mergeCell ref="D9:F9"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.39370078740157483" bottom="0.39370078740157483" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -9824,8 +9796,8 @@
   <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11" style="5" customWidth="1"/>
-    <col min="2" max="2" width="5.625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="11" style="2" customWidth="1"/>
+    <col min="2" max="2" width="5.625" style="2" customWidth="1"/>
     <col min="3" max="3" width="38.875" style="1" customWidth="1"/>
     <col min="4" max="4" width="22.625" style="1" customWidth="1"/>
     <col min="5" max="5" width="11.625" style="1" customWidth="1"/>
@@ -9869,17 +9841,17 @@
       <c r="H3" s="7"/>
     </row>
     <row r="4" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
       <c r="E4" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="13"/>
@@ -9889,7 +9861,7 @@
       </c>
     </row>
     <row r="6" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="14"/>
@@ -9907,13 +9879,13 @@
       <c r="D8" s="9"/>
     </row>
     <row r="9" spans="1:8" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="6" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="10" t="s">
@@ -9921,21 +9893,20 @@
       </c>
       <c r="E9" s="10"/>
       <c r="F9" s="10"/>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="6" t="s">
         <v>12</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="D9:F9"/>
+  <mergeCells count="5">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="B4:C4"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B6:D7"/>
+    <mergeCell ref="D9:F9"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.39370078740157483" bottom="0.39370078740157483" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -9951,8 +9922,8 @@
   <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11" style="5" customWidth="1"/>
-    <col min="2" max="2" width="5.625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="11" style="2" customWidth="1"/>
+    <col min="2" max="2" width="5.625" style="2" customWidth="1"/>
     <col min="3" max="3" width="38.875" style="1" customWidth="1"/>
     <col min="4" max="4" width="22.625" style="1" customWidth="1"/>
     <col min="5" max="5" width="11.625" style="1" customWidth="1"/>
@@ -9996,17 +9967,17 @@
       <c r="H3" s="7"/>
     </row>
     <row r="4" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
       <c r="E4" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="13"/>
@@ -10016,7 +9987,7 @@
       </c>
     </row>
     <row r="6" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="14"/>
@@ -10034,13 +10005,13 @@
       <c r="D8" s="9"/>
     </row>
     <row r="9" spans="1:8" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="6" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="10" t="s">
@@ -10048,21 +10019,20 @@
       </c>
       <c r="E9" s="10"/>
       <c r="F9" s="10"/>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="6" t="s">
         <v>12</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="D9:F9"/>
+  <mergeCells count="5">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="B4:C4"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B6:D7"/>
+    <mergeCell ref="D9:F9"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.39370078740157483" bottom="0.39370078740157483" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -10078,8 +10048,8 @@
   <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11" style="5" customWidth="1"/>
-    <col min="2" max="2" width="5.625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="11" style="2" customWidth="1"/>
+    <col min="2" max="2" width="5.625" style="2" customWidth="1"/>
     <col min="3" max="3" width="38.875" style="1" customWidth="1"/>
     <col min="4" max="4" width="22.625" style="1" customWidth="1"/>
     <col min="5" max="5" width="11.625" style="1" customWidth="1"/>
@@ -10123,17 +10093,17 @@
       <c r="H3" s="7"/>
     </row>
     <row r="4" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
       <c r="E4" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="13"/>
@@ -10143,7 +10113,7 @@
       </c>
     </row>
     <row r="6" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="14"/>
@@ -10161,13 +10131,13 @@
       <c r="D8" s="9"/>
     </row>
     <row r="9" spans="1:8" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="6" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="10" t="s">
@@ -10175,21 +10145,20 @@
       </c>
       <c r="E9" s="10"/>
       <c r="F9" s="10"/>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="6" t="s">
         <v>12</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="D9:F9"/>
+  <mergeCells count="5">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="B4:C4"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B6:D7"/>
+    <mergeCell ref="D9:F9"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.39370078740157483" bottom="0.39370078740157483" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -10205,8 +10174,8 @@
   <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11" style="5" customWidth="1"/>
-    <col min="2" max="2" width="5.625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="11" style="2" customWidth="1"/>
+    <col min="2" max="2" width="5.625" style="2" customWidth="1"/>
     <col min="3" max="3" width="38.875" style="1" customWidth="1"/>
     <col min="4" max="4" width="22.625" style="1" customWidth="1"/>
     <col min="5" max="5" width="11.625" style="1" customWidth="1"/>
@@ -10250,17 +10219,17 @@
       <c r="H3" s="7"/>
     </row>
     <row r="4" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
       <c r="E4" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="13"/>
@@ -10270,7 +10239,7 @@
       </c>
     </row>
     <row r="6" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="14"/>
@@ -10288,13 +10257,13 @@
       <c r="D8" s="9"/>
     </row>
     <row r="9" spans="1:8" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="6" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="10" t="s">
@@ -10302,21 +10271,20 @@
       </c>
       <c r="E9" s="10"/>
       <c r="F9" s="10"/>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="6" t="s">
         <v>12</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="D9:F9"/>
+  <mergeCells count="5">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="B4:C4"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B6:D7"/>
+    <mergeCell ref="D9:F9"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.39370078740157483" bottom="0.39370078740157483" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -10332,8 +10300,8 @@
   <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11" style="5" customWidth="1"/>
-    <col min="2" max="2" width="5.625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="11" style="2" customWidth="1"/>
+    <col min="2" max="2" width="5.625" style="2" customWidth="1"/>
     <col min="3" max="3" width="38.875" style="1" customWidth="1"/>
     <col min="4" max="4" width="22.625" style="1" customWidth="1"/>
     <col min="5" max="5" width="11.625" style="1" customWidth="1"/>
@@ -10377,7 +10345,7 @@
       <c r="H3" s="7"/>
     </row>
     <row r="4" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="12"/>
@@ -10387,7 +10355,7 @@
       </c>
     </row>
     <row r="5" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="13"/>
@@ -10397,7 +10365,7 @@
       </c>
     </row>
     <row r="6" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="14"/>
@@ -10415,13 +10383,13 @@
       <c r="D8" s="9"/>
     </row>
     <row r="9" spans="1:8" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="6" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="10" t="s">
@@ -10429,21 +10397,21 @@
       </c>
       <c r="E9" s="10"/>
       <c r="F9" s="10"/>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="6" t="s">
         <v>12</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="D9:F9"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B6:D7"/>
+    <mergeCell ref="D9:F9"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.39370078740157483" bottom="0.39370078740157483" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -10459,8 +10427,8 @@
   <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11" style="5" customWidth="1"/>
-    <col min="2" max="2" width="5.625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="11" style="2" customWidth="1"/>
+    <col min="2" max="2" width="5.625" style="2" customWidth="1"/>
     <col min="3" max="3" width="38.875" style="1" customWidth="1"/>
     <col min="4" max="4" width="22.625" style="1" customWidth="1"/>
     <col min="5" max="5" width="11.625" style="1" customWidth="1"/>
@@ -10504,7 +10472,7 @@
       <c r="H3" s="7"/>
     </row>
     <row r="4" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="12"/>
@@ -10514,7 +10482,7 @@
       </c>
     </row>
     <row r="5" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="13"/>
@@ -10524,7 +10492,7 @@
       </c>
     </row>
     <row r="6" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="14"/>
@@ -10542,13 +10510,13 @@
       <c r="D8" s="9"/>
     </row>
     <row r="9" spans="1:8" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="6" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="10" t="s">
@@ -10556,21 +10524,21 @@
       </c>
       <c r="E9" s="10"/>
       <c r="F9" s="10"/>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="6" t="s">
         <v>12</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="D9:F9"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B6:D7"/>
+    <mergeCell ref="D9:F9"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.39370078740157483" bottom="0.39370078740157483" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -10586,8 +10554,8 @@
   <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11" style="5" customWidth="1"/>
-    <col min="2" max="2" width="5.625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="11" style="2" customWidth="1"/>
+    <col min="2" max="2" width="5.625" style="2" customWidth="1"/>
     <col min="3" max="3" width="38.875" style="1" customWidth="1"/>
     <col min="4" max="4" width="22.625" style="1" customWidth="1"/>
     <col min="5" max="5" width="11.625" style="1" customWidth="1"/>
@@ -10631,7 +10599,7 @@
       <c r="H3" s="7"/>
     </row>
     <row r="4" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="12"/>
@@ -10641,7 +10609,7 @@
       </c>
     </row>
     <row r="5" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="13"/>
@@ -10651,7 +10619,7 @@
       </c>
     </row>
     <row r="6" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="14"/>
@@ -10669,13 +10637,13 @@
       <c r="D8" s="9"/>
     </row>
     <row r="9" spans="1:8" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="6" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="10" t="s">
@@ -10683,21 +10651,21 @@
       </c>
       <c r="E9" s="10"/>
       <c r="F9" s="10"/>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="6" t="s">
         <v>12</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="D9:F9"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B6:D7"/>
+    <mergeCell ref="D9:F9"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.39370078740157483" bottom="0.39370078740157483" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -10713,8 +10681,8 @@
   <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11" style="5" customWidth="1"/>
-    <col min="2" max="2" width="5.625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="11" style="2" customWidth="1"/>
+    <col min="2" max="2" width="5.625" style="2" customWidth="1"/>
     <col min="3" max="3" width="38.875" style="1" customWidth="1"/>
     <col min="4" max="4" width="22.625" style="1" customWidth="1"/>
     <col min="5" max="5" width="11.625" style="1" customWidth="1"/>
@@ -10758,7 +10726,7 @@
       <c r="H3" s="7"/>
     </row>
     <row r="4" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="12"/>
@@ -10768,7 +10736,7 @@
       </c>
     </row>
     <row r="5" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="13"/>
@@ -10778,7 +10746,7 @@
       </c>
     </row>
     <row r="6" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="14"/>
@@ -10796,13 +10764,13 @@
       <c r="D8" s="9"/>
     </row>
     <row r="9" spans="1:8" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="6" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="10" t="s">
@@ -10810,21 +10778,21 @@
       </c>
       <c r="E9" s="10"/>
       <c r="F9" s="10"/>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="6" t="s">
         <v>12</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="D9:F9"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B6:D7"/>
+    <mergeCell ref="D9:F9"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.39370078740157483" bottom="0.39370078740157483" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -10840,8 +10808,8 @@
   <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11" style="5" customWidth="1"/>
-    <col min="2" max="2" width="5.625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="11" style="2" customWidth="1"/>
+    <col min="2" max="2" width="5.625" style="2" customWidth="1"/>
     <col min="3" max="3" width="38.875" style="1" customWidth="1"/>
     <col min="4" max="4" width="22.625" style="1" customWidth="1"/>
     <col min="5" max="5" width="11.625" style="1" customWidth="1"/>
@@ -10885,7 +10853,7 @@
       <c r="H3" s="7"/>
     </row>
     <row r="4" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="12"/>
@@ -10895,7 +10863,7 @@
       </c>
     </row>
     <row r="5" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="13"/>
@@ -10905,7 +10873,7 @@
       </c>
     </row>
     <row r="6" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="14"/>
@@ -10923,13 +10891,13 @@
       <c r="D8" s="9"/>
     </row>
     <row r="9" spans="1:8" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="6" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="10" t="s">
@@ -10937,21 +10905,21 @@
       </c>
       <c r="E9" s="10"/>
       <c r="F9" s="10"/>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="6" t="s">
         <v>12</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="D9:F9"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B6:D7"/>
+    <mergeCell ref="D9:F9"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.39370078740157483" bottom="0.39370078740157483" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -10967,8 +10935,8 @@
   <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11" style="5" customWidth="1"/>
-    <col min="2" max="2" width="5.625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="11" style="2" customWidth="1"/>
+    <col min="2" max="2" width="5.625" style="2" customWidth="1"/>
     <col min="3" max="3" width="38.875" style="1" customWidth="1"/>
     <col min="4" max="4" width="22.625" style="1" customWidth="1"/>
     <col min="5" max="5" width="11.625" style="1" customWidth="1"/>
@@ -11012,7 +10980,7 @@
       <c r="H3" s="7"/>
     </row>
     <row r="4" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="12"/>
@@ -11022,7 +10990,7 @@
       </c>
     </row>
     <row r="5" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="13"/>
@@ -11032,7 +11000,7 @@
       </c>
     </row>
     <row r="6" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="14"/>
@@ -11050,13 +11018,13 @@
       <c r="D8" s="9"/>
     </row>
     <row r="9" spans="1:8" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="6" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="10" t="s">
@@ -11064,21 +11032,21 @@
       </c>
       <c r="E9" s="10"/>
       <c r="F9" s="10"/>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="6" t="s">
         <v>12</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="D9:F9"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B6:D7"/>
+    <mergeCell ref="D9:F9"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.39370078740157483" bottom="0.39370078740157483" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -11094,8 +11062,8 @@
   <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11" style="5" customWidth="1"/>
-    <col min="2" max="2" width="5.625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="11" style="2" customWidth="1"/>
+    <col min="2" max="2" width="5.625" style="2" customWidth="1"/>
     <col min="3" max="3" width="38.875" style="1" customWidth="1"/>
     <col min="4" max="4" width="22.625" style="1" customWidth="1"/>
     <col min="5" max="5" width="11.625" style="1" customWidth="1"/>
@@ -11139,7 +11107,7 @@
       <c r="H3" s="7"/>
     </row>
     <row r="4" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="12"/>
@@ -11149,7 +11117,7 @@
       </c>
     </row>
     <row r="5" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="13"/>
@@ -11159,7 +11127,7 @@
       </c>
     </row>
     <row r="6" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="14"/>
@@ -11177,13 +11145,13 @@
       <c r="D8" s="9"/>
     </row>
     <row r="9" spans="1:8" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="6" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="10" t="s">
@@ -11191,21 +11159,21 @@
       </c>
       <c r="E9" s="10"/>
       <c r="F9" s="10"/>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="6" t="s">
         <v>12</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="D9:F9"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B6:D7"/>
+    <mergeCell ref="D9:F9"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.39370078740157483" bottom="0.39370078740157483" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -11221,8 +11189,8 @@
   <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11" style="5" customWidth="1"/>
-    <col min="2" max="2" width="5.625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="11" style="2" customWidth="1"/>
+    <col min="2" max="2" width="5.625" style="2" customWidth="1"/>
     <col min="3" max="3" width="38.875" style="1" customWidth="1"/>
     <col min="4" max="4" width="22.625" style="1" customWidth="1"/>
     <col min="5" max="5" width="11.625" style="1" customWidth="1"/>
@@ -11266,17 +11234,17 @@
       <c r="H3" s="7"/>
     </row>
     <row r="4" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
       <c r="E4" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="13"/>
@@ -11286,7 +11254,7 @@
       </c>
     </row>
     <row r="6" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="14"/>
@@ -11304,13 +11272,13 @@
       <c r="D8" s="9"/>
     </row>
     <row r="9" spans="1:8" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="6" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="10" t="s">
@@ -11318,21 +11286,20 @@
       </c>
       <c r="E9" s="10"/>
       <c r="F9" s="10"/>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="6" t="s">
         <v>12</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="D9:F9"/>
+  <mergeCells count="5">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="B4:C4"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B6:D7"/>
+    <mergeCell ref="D9:F9"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.39370078740157483" bottom="0.39370078740157483" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -11348,8 +11315,8 @@
   <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11" style="5" customWidth="1"/>
-    <col min="2" max="2" width="5.625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="11" style="2" customWidth="1"/>
+    <col min="2" max="2" width="5.625" style="2" customWidth="1"/>
     <col min="3" max="3" width="38.875" style="1" customWidth="1"/>
     <col min="4" max="4" width="22.625" style="1" customWidth="1"/>
     <col min="5" max="5" width="11.625" style="1" customWidth="1"/>
@@ -11393,17 +11360,17 @@
       <c r="H3" s="7"/>
     </row>
     <row r="4" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
       <c r="E4" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="13"/>
@@ -11413,7 +11380,7 @@
       </c>
     </row>
     <row r="6" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="14"/>
@@ -11431,13 +11398,13 @@
       <c r="D8" s="9"/>
     </row>
     <row r="9" spans="1:8" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="6" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="10" t="s">
@@ -11445,21 +11412,20 @@
       </c>
       <c r="E9" s="10"/>
       <c r="F9" s="10"/>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="6" t="s">
         <v>12</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="D9:F9"/>
+  <mergeCells count="5">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="B4:C4"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B6:D7"/>
+    <mergeCell ref="D9:F9"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.39370078740157483" bottom="0.39370078740157483" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -11475,8 +11441,8 @@
   <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11" style="5" customWidth="1"/>
-    <col min="2" max="2" width="5.625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="11" style="2" customWidth="1"/>
+    <col min="2" max="2" width="5.625" style="2" customWidth="1"/>
     <col min="3" max="3" width="38.875" style="1" customWidth="1"/>
     <col min="4" max="4" width="22.625" style="1" customWidth="1"/>
     <col min="5" max="5" width="11.625" style="1" customWidth="1"/>
@@ -11520,17 +11486,17 @@
       <c r="H3" s="7"/>
     </row>
     <row r="4" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
       <c r="E4" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="13"/>
@@ -11540,7 +11506,7 @@
       </c>
     </row>
     <row r="6" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="14"/>
@@ -11558,13 +11524,13 @@
       <c r="D8" s="9"/>
     </row>
     <row r="9" spans="1:8" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="6" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="10" t="s">
@@ -11572,21 +11538,20 @@
       </c>
       <c r="E9" s="10"/>
       <c r="F9" s="10"/>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="6" t="s">
         <v>12</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="D9:F9"/>
+  <mergeCells count="5">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="B4:C4"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B6:D7"/>
+    <mergeCell ref="D9:F9"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.39370078740157483" bottom="0.39370078740157483" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -11602,8 +11567,8 @@
   <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11" style="5" customWidth="1"/>
-    <col min="2" max="2" width="5.625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="11" style="2" customWidth="1"/>
+    <col min="2" max="2" width="5.625" style="2" customWidth="1"/>
     <col min="3" max="3" width="38.875" style="1" customWidth="1"/>
     <col min="4" max="4" width="22.625" style="1" customWidth="1"/>
     <col min="5" max="5" width="11.625" style="1" customWidth="1"/>
@@ -11647,17 +11612,17 @@
       <c r="H3" s="7"/>
     </row>
     <row r="4" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
       <c r="E4" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="13"/>
@@ -11667,7 +11632,7 @@
       </c>
     </row>
     <row r="6" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="14"/>
@@ -11685,13 +11650,13 @@
       <c r="D8" s="9"/>
     </row>
     <row r="9" spans="1:8" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="6" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="10" t="s">
@@ -11699,21 +11664,20 @@
       </c>
       <c r="E9" s="10"/>
       <c r="F9" s="10"/>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="6" t="s">
         <v>12</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="D9:F9"/>
+  <mergeCells count="5">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="B4:C4"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B6:D7"/>
+    <mergeCell ref="D9:F9"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.39370078740157483" bottom="0.39370078740157483" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -11729,8 +11693,8 @@
   <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11" style="5" customWidth="1"/>
-    <col min="2" max="2" width="5.625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="11" style="2" customWidth="1"/>
+    <col min="2" max="2" width="5.625" style="2" customWidth="1"/>
     <col min="3" max="3" width="38.875" style="1" customWidth="1"/>
     <col min="4" max="4" width="22.625" style="1" customWidth="1"/>
     <col min="5" max="5" width="11.625" style="1" customWidth="1"/>
@@ -11774,7 +11738,7 @@
       <c r="H3" s="7"/>
     </row>
     <row r="4" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="12"/>
@@ -11784,7 +11748,7 @@
       </c>
     </row>
     <row r="5" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="13"/>
@@ -11794,7 +11758,7 @@
       </c>
     </row>
     <row r="6" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="14"/>
@@ -11812,13 +11776,13 @@
       <c r="D8" s="9"/>
     </row>
     <row r="9" spans="1:8" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="6" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="10" t="s">
@@ -11826,21 +11790,21 @@
       </c>
       <c r="E9" s="10"/>
       <c r="F9" s="10"/>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="6" t="s">
         <v>12</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="D9:F9"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B6:D7"/>
+    <mergeCell ref="D9:F9"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.39370078740157483" bottom="0.39370078740157483" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -11856,8 +11820,8 @@
   <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11" style="5" customWidth="1"/>
-    <col min="2" max="2" width="5.625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="11" style="2" customWidth="1"/>
+    <col min="2" max="2" width="5.625" style="2" customWidth="1"/>
     <col min="3" max="3" width="38.875" style="1" customWidth="1"/>
     <col min="4" max="4" width="22.625" style="1" customWidth="1"/>
     <col min="5" max="5" width="11.625" style="1" customWidth="1"/>
@@ -11901,7 +11865,7 @@
       <c r="H3" s="7"/>
     </row>
     <row r="4" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="12"/>
@@ -11911,7 +11875,7 @@
       </c>
     </row>
     <row r="5" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="13"/>
@@ -11921,7 +11885,7 @@
       </c>
     </row>
     <row r="6" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="14"/>
@@ -11939,13 +11903,13 @@
       <c r="D8" s="9"/>
     </row>
     <row r="9" spans="1:8" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="6" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="10" t="s">
@@ -11953,21 +11917,21 @@
       </c>
       <c r="E9" s="10"/>
       <c r="F9" s="10"/>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="6" t="s">
         <v>12</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="D9:F9"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B6:D7"/>
+    <mergeCell ref="D9:F9"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.39370078740157483" bottom="0.39370078740157483" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -11983,8 +11947,8 @@
   <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11" style="5" customWidth="1"/>
-    <col min="2" max="2" width="5.625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="11" style="2" customWidth="1"/>
+    <col min="2" max="2" width="5.625" style="2" customWidth="1"/>
     <col min="3" max="3" width="38.875" style="1" customWidth="1"/>
     <col min="4" max="4" width="22.625" style="1" customWidth="1"/>
     <col min="5" max="5" width="11.625" style="1" customWidth="1"/>
@@ -12028,7 +11992,7 @@
       <c r="H3" s="7"/>
     </row>
     <row r="4" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="12"/>
@@ -12038,7 +12002,7 @@
       </c>
     </row>
     <row r="5" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="13"/>
@@ -12048,7 +12012,7 @@
       </c>
     </row>
     <row r="6" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="14"/>
@@ -12066,13 +12030,13 @@
       <c r="D8" s="9"/>
     </row>
     <row r="9" spans="1:8" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="6" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="10" t="s">
@@ -12080,21 +12044,21 @@
       </c>
       <c r="E9" s="10"/>
       <c r="F9" s="10"/>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="6" t="s">
         <v>12</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="D9:F9"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B6:D7"/>
+    <mergeCell ref="D9:F9"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.39370078740157483" bottom="0.39370078740157483" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -12110,8 +12074,8 @@
   <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11" style="5" customWidth="1"/>
-    <col min="2" max="2" width="5.625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="11" style="2" customWidth="1"/>
+    <col min="2" max="2" width="5.625" style="2" customWidth="1"/>
     <col min="3" max="3" width="38.875" style="1" customWidth="1"/>
     <col min="4" max="4" width="22.625" style="1" customWidth="1"/>
     <col min="5" max="5" width="11.625" style="1" customWidth="1"/>
@@ -12155,7 +12119,7 @@
       <c r="H3" s="7"/>
     </row>
     <row r="4" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="12"/>
@@ -12165,7 +12129,7 @@
       </c>
     </row>
     <row r="5" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="13"/>
@@ -12175,7 +12139,7 @@
       </c>
     </row>
     <row r="6" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="14"/>
@@ -12193,13 +12157,13 @@
       <c r="D8" s="9"/>
     </row>
     <row r="9" spans="1:8" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="6" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="10" t="s">
@@ -12207,21 +12171,21 @@
       </c>
       <c r="E9" s="10"/>
       <c r="F9" s="10"/>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="6" t="s">
         <v>12</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="D9:F9"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B6:D7"/>
+    <mergeCell ref="D9:F9"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.39370078740157483" bottom="0.39370078740157483" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -12237,8 +12201,8 @@
   <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11" style="5" customWidth="1"/>
-    <col min="2" max="2" width="5.625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="11" style="2" customWidth="1"/>
+    <col min="2" max="2" width="5.625" style="2" customWidth="1"/>
     <col min="3" max="3" width="38.875" style="1" customWidth="1"/>
     <col min="4" max="4" width="22.625" style="1" customWidth="1"/>
     <col min="5" max="5" width="11.625" style="1" customWidth="1"/>
@@ -12282,7 +12246,7 @@
       <c r="H3" s="7"/>
     </row>
     <row r="4" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="12"/>
@@ -12292,7 +12256,7 @@
       </c>
     </row>
     <row r="5" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="13"/>
@@ -12302,7 +12266,7 @@
       </c>
     </row>
     <row r="6" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="14"/>
@@ -12320,13 +12284,13 @@
       <c r="D8" s="9"/>
     </row>
     <row r="9" spans="1:8" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="6" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="10" t="s">
@@ -12334,21 +12298,21 @@
       </c>
       <c r="E9" s="10"/>
       <c r="F9" s="10"/>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="6" t="s">
         <v>12</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="D9:F9"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B6:D7"/>
+    <mergeCell ref="D9:F9"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.39370078740157483" bottom="0.39370078740157483" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -12364,8 +12328,8 @@
   <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11" style="5" customWidth="1"/>
-    <col min="2" max="2" width="5.625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="11" style="2" customWidth="1"/>
+    <col min="2" max="2" width="5.625" style="2" customWidth="1"/>
     <col min="3" max="3" width="38.875" style="1" customWidth="1"/>
     <col min="4" max="4" width="22.625" style="1" customWidth="1"/>
     <col min="5" max="5" width="11.625" style="1" customWidth="1"/>
@@ -12409,7 +12373,7 @@
       <c r="H3" s="7"/>
     </row>
     <row r="4" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="12"/>
@@ -12419,7 +12383,7 @@
       </c>
     </row>
     <row r="5" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="13"/>
@@ -12429,7 +12393,7 @@
       </c>
     </row>
     <row r="6" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="14"/>
@@ -12447,13 +12411,13 @@
       <c r="D8" s="9"/>
     </row>
     <row r="9" spans="1:8" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="6" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="10" t="s">
@@ -12461,21 +12425,21 @@
       </c>
       <c r="E9" s="10"/>
       <c r="F9" s="10"/>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="6" t="s">
         <v>12</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="D9:F9"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B6:D7"/>
+    <mergeCell ref="D9:F9"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.39370078740157483" bottom="0.39370078740157483" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -12491,8 +12455,8 @@
   <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11" style="5" customWidth="1"/>
-    <col min="2" max="2" width="5.625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="11" style="2" customWidth="1"/>
+    <col min="2" max="2" width="5.625" style="2" customWidth="1"/>
     <col min="3" max="3" width="38.875" style="1" customWidth="1"/>
     <col min="4" max="4" width="22.625" style="1" customWidth="1"/>
     <col min="5" max="5" width="11.625" style="1" customWidth="1"/>
@@ -12536,7 +12500,7 @@
       <c r="H3" s="7"/>
     </row>
     <row r="4" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="12"/>
@@ -12546,7 +12510,7 @@
       </c>
     </row>
     <row r="5" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="13"/>
@@ -12556,7 +12520,7 @@
       </c>
     </row>
     <row r="6" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="14"/>
@@ -12574,13 +12538,13 @@
       <c r="D8" s="9"/>
     </row>
     <row r="9" spans="1:8" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="6" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="10" t="s">
@@ -12588,21 +12552,21 @@
       </c>
       <c r="E9" s="10"/>
       <c r="F9" s="10"/>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="6" t="s">
         <v>12</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="D9:F9"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B6:D7"/>
+    <mergeCell ref="D9:F9"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.39370078740157483" bottom="0.39370078740157483" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -12618,8 +12582,8 @@
   <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11" style="5" customWidth="1"/>
-    <col min="2" max="2" width="5.625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="11" style="2" customWidth="1"/>
+    <col min="2" max="2" width="5.625" style="2" customWidth="1"/>
     <col min="3" max="3" width="38.875" style="1" customWidth="1"/>
     <col min="4" max="4" width="22.625" style="1" customWidth="1"/>
     <col min="5" max="5" width="11.625" style="1" customWidth="1"/>
@@ -12663,17 +12627,17 @@
       <c r="H3" s="7"/>
     </row>
     <row r="4" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
       <c r="E4" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="13"/>
@@ -12683,7 +12647,7 @@
       </c>
     </row>
     <row r="6" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="14"/>
@@ -12701,13 +12665,13 @@
       <c r="D8" s="9"/>
     </row>
     <row r="9" spans="1:8" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="6" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="10" t="s">
@@ -12715,21 +12679,20 @@
       </c>
       <c r="E9" s="10"/>
       <c r="F9" s="10"/>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="6" t="s">
         <v>12</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="D9:F9"/>
+  <mergeCells count="5">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="B4:C4"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B6:D7"/>
+    <mergeCell ref="D9:F9"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.39370078740157483" bottom="0.39370078740157483" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -12745,8 +12708,8 @@
   <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11" style="5" customWidth="1"/>
-    <col min="2" max="2" width="5.625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="11" style="2" customWidth="1"/>
+    <col min="2" max="2" width="5.625" style="2" customWidth="1"/>
     <col min="3" max="3" width="38.875" style="1" customWidth="1"/>
     <col min="4" max="4" width="22.625" style="1" customWidth="1"/>
     <col min="5" max="5" width="11.625" style="1" customWidth="1"/>
@@ -12790,17 +12753,17 @@
       <c r="H3" s="7"/>
     </row>
     <row r="4" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
       <c r="E4" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="13"/>
@@ -12810,7 +12773,7 @@
       </c>
     </row>
     <row r="6" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="14"/>
@@ -12828,13 +12791,13 @@
       <c r="D8" s="9"/>
     </row>
     <row r="9" spans="1:8" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="6" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="10" t="s">
@@ -12842,21 +12805,20 @@
       </c>
       <c r="E9" s="10"/>
       <c r="F9" s="10"/>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="6" t="s">
         <v>12</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="D9:F9"/>
+  <mergeCells count="5">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="B4:C4"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B6:D7"/>
+    <mergeCell ref="D9:F9"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.39370078740157483" bottom="0.39370078740157483" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -12872,8 +12834,8 @@
   <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11" style="5" customWidth="1"/>
-    <col min="2" max="2" width="5.625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="11" style="2" customWidth="1"/>
+    <col min="2" max="2" width="5.625" style="2" customWidth="1"/>
     <col min="3" max="3" width="38.875" style="1" customWidth="1"/>
     <col min="4" max="4" width="22.625" style="1" customWidth="1"/>
     <col min="5" max="5" width="11.625" style="1" customWidth="1"/>
@@ -12917,17 +12879,17 @@
       <c r="H3" s="7"/>
     </row>
     <row r="4" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
       <c r="E4" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="13"/>
@@ -12937,7 +12899,7 @@
       </c>
     </row>
     <row r="6" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="14"/>
@@ -12955,13 +12917,13 @@
       <c r="D8" s="9"/>
     </row>
     <row r="9" spans="1:8" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="6" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="10" t="s">
@@ -12969,21 +12931,20 @@
       </c>
       <c r="E9" s="10"/>
       <c r="F9" s="10"/>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="6" t="s">
         <v>12</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="D9:F9"/>
+  <mergeCells count="5">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="B4:C4"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B6:D7"/>
+    <mergeCell ref="D9:F9"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.39370078740157483" bottom="0.39370078740157483" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -12999,8 +12960,8 @@
   <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11" style="5" customWidth="1"/>
-    <col min="2" max="2" width="5.625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="11" style="2" customWidth="1"/>
+    <col min="2" max="2" width="5.625" style="2" customWidth="1"/>
     <col min="3" max="3" width="38.875" style="1" customWidth="1"/>
     <col min="4" max="4" width="22.625" style="1" customWidth="1"/>
     <col min="5" max="5" width="11.625" style="1" customWidth="1"/>
@@ -13044,17 +13005,17 @@
       <c r="H3" s="7"/>
     </row>
     <row r="4" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
       <c r="E4" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="13"/>
@@ -13064,7 +13025,7 @@
       </c>
     </row>
     <row r="6" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="14"/>
@@ -13082,13 +13043,13 @@
       <c r="D8" s="9"/>
     </row>
     <row r="9" spans="1:8" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="6" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="10" t="s">
@@ -13096,21 +13057,20 @@
       </c>
       <c r="E9" s="10"/>
       <c r="F9" s="10"/>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="6" t="s">
         <v>12</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="D9:F9"/>
+  <mergeCells count="5">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="B4:C4"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B6:D7"/>
+    <mergeCell ref="D9:F9"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.39370078740157483" bottom="0.39370078740157483" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -13126,8 +13086,8 @@
   <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11" style="5" customWidth="1"/>
-    <col min="2" max="2" width="5.625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="11" style="2" customWidth="1"/>
+    <col min="2" max="2" width="5.625" style="2" customWidth="1"/>
     <col min="3" max="3" width="38.875" style="1" customWidth="1"/>
     <col min="4" max="4" width="22.625" style="1" customWidth="1"/>
     <col min="5" max="5" width="11.625" style="1" customWidth="1"/>
@@ -13171,7 +13131,7 @@
       <c r="H3" s="7"/>
     </row>
     <row r="4" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="12"/>
@@ -13181,7 +13141,7 @@
       </c>
     </row>
     <row r="5" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="13"/>
@@ -13191,7 +13151,7 @@
       </c>
     </row>
     <row r="6" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="14"/>
@@ -13209,13 +13169,13 @@
       <c r="D8" s="9"/>
     </row>
     <row r="9" spans="1:8" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="6" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="10" t="s">
@@ -13223,21 +13183,21 @@
       </c>
       <c r="E9" s="10"/>
       <c r="F9" s="10"/>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="6" t="s">
         <v>12</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="D9:F9"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B6:D7"/>
+    <mergeCell ref="D9:F9"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.39370078740157483" bottom="0.39370078740157483" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -13253,8 +13213,8 @@
   <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11" style="5" customWidth="1"/>
-    <col min="2" max="2" width="5.625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="11" style="2" customWidth="1"/>
+    <col min="2" max="2" width="5.625" style="2" customWidth="1"/>
     <col min="3" max="3" width="38.875" style="1" customWidth="1"/>
     <col min="4" max="4" width="22.625" style="1" customWidth="1"/>
     <col min="5" max="5" width="11.625" style="1" customWidth="1"/>
@@ -13298,7 +13258,7 @@
       <c r="H3" s="7"/>
     </row>
     <row r="4" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="12"/>
@@ -13308,7 +13268,7 @@
       </c>
     </row>
     <row r="5" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="13"/>
@@ -13318,7 +13278,7 @@
       </c>
     </row>
     <row r="6" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="14"/>
@@ -13336,13 +13296,13 @@
       <c r="D8" s="9"/>
     </row>
     <row r="9" spans="1:8" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="6" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="10" t="s">
@@ -13350,21 +13310,21 @@
       </c>
       <c r="E9" s="10"/>
       <c r="F9" s="10"/>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="6" t="s">
         <v>12</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="D9:F9"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B6:D7"/>
+    <mergeCell ref="D9:F9"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.39370078740157483" bottom="0.39370078740157483" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -13380,8 +13340,8 @@
   <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11" style="5" customWidth="1"/>
-    <col min="2" max="2" width="5.625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="11" style="2" customWidth="1"/>
+    <col min="2" max="2" width="5.625" style="2" customWidth="1"/>
     <col min="3" max="3" width="38.875" style="1" customWidth="1"/>
     <col min="4" max="4" width="22.625" style="1" customWidth="1"/>
     <col min="5" max="5" width="11.625" style="1" customWidth="1"/>
@@ -13425,7 +13385,7 @@
       <c r="H3" s="7"/>
     </row>
     <row r="4" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="12"/>
@@ -13435,7 +13395,7 @@
       </c>
     </row>
     <row r="5" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="13"/>
@@ -13445,7 +13405,7 @@
       </c>
     </row>
     <row r="6" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="14"/>
@@ -13463,13 +13423,13 @@
       <c r="D8" s="9"/>
     </row>
     <row r="9" spans="1:8" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="6" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="10" t="s">
@@ -13477,21 +13437,21 @@
       </c>
       <c r="E9" s="10"/>
       <c r="F9" s="10"/>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="6" t="s">
         <v>12</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="D9:F9"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B6:D7"/>
+    <mergeCell ref="D9:F9"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.39370078740157483" bottom="0.39370078740157483" header="0.19685039370078741" footer="0.19685039370078741"/>
